--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15890-2026</t>
+          <t>A 7903-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46107</v>
+        <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -1524,12 +1524,128 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
+        <v>20</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Björksplintborre
+Guldlockmossa
+Platt fjädermossa
+Spillkråka
+Kungsfågel
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15890-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
         <v>10</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>10</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -1541,152 +1657,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7903-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45350</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>20</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Björksplintborre
-Guldlockmossa
-Platt fjädermossa
-Spillkråka
-Kungsfågel
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>46235</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26491-2024</t>
+          <t>A 63575-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45469</v>
+        <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,125 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Stor revmossa
+Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26491-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Gulpudrad spiklav
@@ -2346,149 +2459,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 63575-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Stor revmossa
-Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
         <v/>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>45728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58954-2022</t>
+          <t>A 11516-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,348 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes
+Vildkaprifol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33802-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik
+Björksplintborre
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 47330-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Älg
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 47330-2025 artfynd.xlsx", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 47330-2025 karta.png", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 47330-2025 georefererad karta.tif", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 47330-2025 FSC-klagomål.docx", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 47330-2025 FSC-klagomål mail.docx", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 47330-2025 tillsynsbegäran.docx", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 47330-2025 tillsynsbegäran mail.docx", "A 47330-2025")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 47330-2025 prioriterade fågelarter.docx", "A 47330-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 58954-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44903</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U23" t="n">
         <v>9</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Blåmossa
@@ -2797,372 +3133,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11516-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes
-Vildkaprifol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 47330-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45930</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>7</v>
-      </c>
-      <c r="U22" t="n">
-        <v>7</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Älg
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 47330-2025 artfynd.xlsx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 47330-2025 karta.png", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 47330-2025 georefererad karta.tif", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 47330-2025 FSC-klagomål.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 47330-2025 FSC-klagomål mail.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 47330-2025 tillsynsbegäran.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 47330-2025 tillsynsbegäran mail.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 47330-2025 prioriterade fågelarter.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 33802-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>11</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik
-Björksplintborre
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
         <v/>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         <v>45123</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14048-2026</t>
+          <t>A 37461-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46099</v>
+        <v>45540</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3347,163 +3347,163 @@
         <v>3</v>
       </c>
       <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Gulnål
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 14048-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>3</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 37461-2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Gulnål
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16534-2025</t>
+          <t>A 1503-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45751</v>
+        <v>45306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,16 +3533,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3566,1029 +3566,1029 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 16534-2025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
         <v>3</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 20586-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45057</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>1.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>A 380-2025</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>45662</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E31" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>8.6</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>2</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>A 13306-2026</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>46094</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E32" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T32" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Åkergroda</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 63569-2023</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45275</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>2.4</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 3413-2023</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>44949</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>2.3</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U35" t="n">
         <v>3</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda
 Revlummer</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 12982-2024</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>45385</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E36" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>3.3</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U36" t="n">
         <v>1</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Orre
 Revlummer</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 13380-2025</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45735</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>5</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" t="n">
-        <v>4</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
         <v/>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
         <v>45595</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41607-2022</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44827</v>
+        <v>46007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4767,50 +4767,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4824,10 +4820,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45394</v>
+        <v>45810</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4840,13 +4836,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4876,50 +4872,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4933,10 +4925,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45737</v>
+        <v>45712</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4949,7 +4941,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4989,42 +4981,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 41607-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5038,10 +5030,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46072</v>
+        <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5054,7 +5046,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5094,42 +5086,46 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5143,10 +5139,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44564</v>
+        <v>45331</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5159,13 +5155,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5195,50 +5191,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5252,10 +5244,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45954</v>
+        <v>45737</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5268,7 +5260,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5308,46 +5300,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5361,10 +5349,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46007</v>
+        <v>46072</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5377,7 +5365,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5413,46 +5401,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5466,10 +5454,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45712</v>
+        <v>45954</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5482,7 +5470,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5522,42 +5510,46 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5571,10 +5563,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44827</v>
+        <v>44564</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5587,7 +5579,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5627,42 +5619,46 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5672,14 +5668,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45469</v>
+        <v>46245</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,13 +5688,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5725,49 +5721,49 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5777,14 +5773,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45518</v>
+        <v>45325</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5800,7 +5796,7 @@
         <v>0.6</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -5809,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -5821,10 +5817,10 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -5837,42 +5833,46 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE48">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5882,14 +5882,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46245</v>
+        <v>45469</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,13 +5902,13 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5935,49 +5935,49 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5987,14 +5987,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45325</v>
+        <v>45394</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -6043,50 +6043,50 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AE50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45810</v>
+        <v>45518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6116,20 +6116,20 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>1</v>
       </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6156,42 +6156,42 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45331</v>
+        <v>44827</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6221,13 +6221,13 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6257,39 +6257,39 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
         <v>45011</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44504</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44662</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44468</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45230</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45091</v>
+        <v>44967</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44805</v>
+        <v>45307</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44480</v>
+        <v>44949</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 49955-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44963</v>
+        <v>44456</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44949</v>
+        <v>45043</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7496,7 +7496,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45222</v>
+        <v>45257</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45535</v>
+        <v>45308</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44475</v>
+        <v>44662</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7715,7 +7715,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7729,10 +7729,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44727</v>
+        <v>45230</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>1.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45737</v>
+        <v>46036</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7861,7 +7861,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45833</v>
+        <v>44475</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45833</v>
+        <v>45737</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45833</v>
+        <v>45603</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8080,7 +8080,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45091</v>
+        <v>45833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46077</v>
+        <v>45833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45924</v>
+        <v>45833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49955-2021</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44456</v>
+        <v>44480</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44896</v>
+        <v>46056</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44573</v>
+        <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44638</v>
+        <v>46058</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44802</v>
+        <v>44727</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45943</v>
+        <v>46062</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8737,7 +8737,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45947</v>
+        <v>46062</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>12</v>
+        <v>0.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8810,7 +8810,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45952</v>
+        <v>46062</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45755</v>
+        <v>44573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8956,7 +8956,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46118</v>
+        <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45978</v>
+        <v>44896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9102,7 +9102,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44858</v>
+        <v>45123</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45306</v>
+        <v>46077</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9248,7 +9248,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45833</v>
+        <v>45943</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45596</v>
+        <v>45222</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9394,7 +9394,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45989</v>
+        <v>45947</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45994</v>
+        <v>45091</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9540,7 +9540,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9554,10 +9554,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46134</v>
+        <v>45952</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46002</v>
+        <v>45196</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9686,7 +9686,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46002</v>
+        <v>46118</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9759,7 +9759,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45804</v>
+        <v>46134</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9832,7 +9832,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44973</v>
+        <v>45978</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44887</v>
+        <v>44963</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9978,7 +9978,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9992,10 +9992,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46036</v>
+        <v>45833</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45180</v>
+        <v>45989</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46008</v>
+        <v>44510</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10197,7 +10197,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44523</v>
+        <v>45994</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10270,7 +10270,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45894</v>
+        <v>44523</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45028</v>
+        <v>46002</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10416,7 +10416,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45123</v>
+        <v>46002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10489,7 +10489,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10499,14 +10499,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45394</v>
+        <v>45894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10562,7 +10562,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46056</v>
+        <v>46008</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10645,14 +10645,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46058</v>
+        <v>45804</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46062</v>
+        <v>44585</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10781,7 +10781,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46062</v>
+        <v>44515</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10868,10 +10868,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46062</v>
+        <v>45755</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10941,10 +10941,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45196</v>
+        <v>44887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45328</v>
+        <v>46154</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11087,10 +11087,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44656</v>
+        <v>45535</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44585</v>
+        <v>45931</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46154</v>
+        <v>46195</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45189</v>
+        <v>46195</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.1</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45350</v>
+        <v>45747</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45603</v>
+        <v>45350</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11528,7 +11528,7 @@
         <v>45327</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44546</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11676,10 +11676,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45931</v>
+        <v>45523</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11735,7 +11735,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45307</v>
+        <v>45091</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11808,7 +11808,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11822,10 +11822,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45744</v>
+        <v>45028</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11881,7 +11881,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11895,10 +11895,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46195</v>
+        <v>45054</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11954,7 +11954,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11968,10 +11968,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46195</v>
+        <v>44858</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12041,10 +12041,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45524</v>
+        <v>45559</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12114,10 +12114,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45559</v>
+        <v>44973</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12173,7 +12173,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12187,10 +12187,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44662</v>
+        <v>44802</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45308</v>
+        <v>45306</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12319,7 +12319,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12333,10 +12333,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44949</v>
+        <v>45306</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12392,7 +12392,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12402,14 +12402,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44515</v>
+        <v>45394</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12475,14 +12475,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44636</v>
+        <v>45180</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12538,7 +12538,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12548,14 +12548,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44585</v>
+        <v>44636</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>0.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12611,7 +12611,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12625,10 +12625,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44963</v>
+        <v>44805</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12684,7 +12684,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45523</v>
+        <v>44949</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12757,7 +12757,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12771,10 +12771,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45054</v>
+        <v>45744</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12830,7 +12830,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45306</v>
+        <v>45596</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12903,7 +12903,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12917,10 +12917,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44967</v>
+        <v>45524</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12976,7 +12976,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44510</v>
+        <v>44656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5.7</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13063,10 +13063,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45747</v>
+        <v>45328</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13122,7 +13122,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13136,10 +13136,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45790</v>
+        <v>44963</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45329</v>
+        <v>44585</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13282,10 +13282,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45043</v>
+        <v>45329</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45257</v>
+        <v>45790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13431,7 +13431,7 @@
         <v>44713</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45894</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 7903-2024</t>
+          <t>A 15890-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45350</v>
+        <v>46107</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -1524,12 +1524,128 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Björksplintborre
+Spillkråka
+Späd frullania
+Kungsfågel
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 7903-2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
         <v>20</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>20</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita
@@ -1541,152 +1657,36 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15890-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>10</v>
-      </c>
-      <c r="U10" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Björksplintborre
-Spillkråka
-Späd frullania
-Kungsfågel
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24162-2025</t>
+          <t>A 32151-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45796</v>
+        <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2102,12 +2102,127 @@
         <v>7</v>
       </c>
       <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Talltita
+Blåmossa
+Västlig hakmossa
+Spillkråka
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 24162-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
         <v>19</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>19</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Blanksvart trämyra
@@ -2118,158 +2233,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 32151-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Talltita
-Blåmossa
-Västlig hakmossa
-Spillkråka
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63575-2023</t>
+          <t>A 26491-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45275</v>
+        <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,238 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Gulpudrad spiklav
+Rostfläck
+Sotlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 12084-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka
+Kungsfågel
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 63575-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
         <v>7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -2346,262 +2572,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26491-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45469</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Gulpudrad spiklav
-Rostfläck
-Sotlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 12084-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka
-Kungsfågel
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11516-2026</t>
+          <t>A 58954-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46083</v>
+        <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,124 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Blåmossa
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 11516-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>6</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes
@@ -2797,111 +2909,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 33802-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>5.8</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>11</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Kortskaftad ärgspik
 Björksplintborre
@@ -2909,111 +3021,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 47330-2025</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>3.7</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>7</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>7</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Älg
@@ -3021,148 +3133,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 47330-2025 artfynd.xlsx", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 47330-2025 karta.png", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 47330-2025 georefererad karta.tif", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 47330-2025 FSC-klagomål.docx", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 47330-2025 FSC-klagomål mail.docx", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 47330-2025 tillsynsbegäran.docx", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 47330-2025 tillsynsbegäran mail.docx", "A 47330-2025")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 47330-2025 prioriterade fågelarter.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 58954-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44903</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>9</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Blåmossa
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
         <v/>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         <v>45123</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37461-2024</t>
+          <t>A 14048-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45540</v>
+        <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3347,163 +3347,163 @@
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 37461-2024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45540</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Gulnål
 Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 14048-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46099</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1503-2024</t>
+          <t>A 13306-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45306</v>
+        <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -3566,1029 +3566,1029 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Åkergroda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 63569-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
         <v>4</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>4</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 3413-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 12982-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Orre
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 1503-2024</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="D33" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 16534-2025</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>45751</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>1.5</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 20586-2023</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45057</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>1.5</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U35" t="n">
         <v>3</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 380-2025</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>45662</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E36" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>8.6</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U36" t="n">
         <v>2</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 13306-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Åkergroda</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 63569-2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 13380-2025</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45735</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>5</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 3413-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>44949</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 12982-2024</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45385</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Orre
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
         <v/>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
         <v>45595</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 41607-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46007</v>
+        <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4767,46 +4767,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4820,10 +4824,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45810</v>
+        <v>45394</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4836,13 +4840,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4872,46 +4876,50 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4925,10 +4933,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45712</v>
+        <v>45954</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4941,7 +4949,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4981,42 +4989,46 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41607-2022</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5030,10 +5042,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44827</v>
+        <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5046,7 +5058,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5090,42 +5102,42 @@
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5139,10 +5151,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45331</v>
+        <v>46007</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,13 +5167,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5195,42 +5207,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5244,10 +5256,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45737</v>
+        <v>45712</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5260,7 +5272,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5300,35 +5312,35 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
@@ -5352,7 +5364,7 @@
         <v>46072</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5440,7 +5452,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5454,10 +5466,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45954</v>
+        <v>44827</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5470,7 +5482,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5506,50 +5518,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5559,14 +5567,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44564</v>
+        <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5579,7 +5587,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5612,46 +5620,42 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
@@ -5675,7 +5679,7 @@
         <v>46245</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5780,7 +5784,7 @@
         <v>45325</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5872,7 +5876,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5882,14 +5886,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45469</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,20 +5906,20 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -5926,58 +5930,58 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5991,10 +5995,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45394</v>
+        <v>45810</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6007,13 +6011,13 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6043,50 +6047,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
-        <v/>
-      </c>
-      <c r="AE50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45518</v>
+        <v>45331</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6116,19 +6116,19 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6152,46 +6152,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44827</v>
+        <v>45737</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6257,39 +6257,39 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
         <v>45011</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44504</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15508-2022</t>
+          <t>A 53144-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44662</v>
+        <v>44468</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6912,7 +6912,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53144-2021</t>
+          <t>A 20285-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44468</v>
+        <v>44698</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20285-2022</t>
+          <t>A 15508-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44698</v>
+        <v>44662</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7058,7 +7058,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>45091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44967</v>
+        <v>45307</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45307</v>
+        <v>45230</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44949</v>
+        <v>45744</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 49955-2021</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44456</v>
+        <v>44805</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 49955-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45043</v>
+        <v>44456</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7496,7 +7496,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45257</v>
+        <v>44480</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45308</v>
+        <v>44963</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44662</v>
+        <v>44949</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7715,7 +7715,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7729,10 +7729,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45230</v>
+        <v>45222</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46036</v>
+        <v>45535</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
         <v>44475</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45737</v>
+        <v>46118</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45603</v>
+        <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8080,7 +8080,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45833</v>
+        <v>45524</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45833</v>
+        <v>44727</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45833</v>
+        <v>44896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44480</v>
+        <v>44573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46056</v>
+        <v>44638</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8445,7 +8445,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45924</v>
+        <v>45559</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.3</v>
+        <v>8.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46058</v>
+        <v>46134</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44727</v>
+        <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46062</v>
+        <v>45947</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>12</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8737,7 +8737,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46062</v>
+        <v>44662</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8810,7 +8810,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46062</v>
+        <v>45952</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44573</v>
+        <v>45804</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8956,7 +8956,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44638</v>
+        <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44896</v>
+        <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9102,7 +9102,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45123</v>
+        <v>45894</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46077</v>
+        <v>45978</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9248,7 +9248,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45943</v>
+        <v>44802</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45222</v>
+        <v>45833</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9394,7 +9394,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45947</v>
+        <v>45308</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>12</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45091</v>
+        <v>45989</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9540,7 +9540,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9554,10 +9554,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45952</v>
+        <v>44949</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45196</v>
+        <v>45994</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9686,7 +9686,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46118</v>
+        <v>44515</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9759,7 +9759,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46134</v>
+        <v>44636</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9832,7 +9832,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45978</v>
+        <v>45755</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44963</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9978,7 +9978,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9992,10 +9992,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45833</v>
+        <v>46002</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45989</v>
+        <v>46154</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44510</v>
+        <v>44858</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10197,7 +10197,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45994</v>
+        <v>44585</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10270,7 +10270,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44523</v>
+        <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46002</v>
+        <v>45306</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10416,7 +10416,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46002</v>
+        <v>45596</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10489,7 +10489,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45894</v>
+        <v>45931</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10562,7 +10562,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46008</v>
+        <v>46056</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10645,14 +10645,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45804</v>
+        <v>46058</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44585</v>
+        <v>46062</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10781,7 +10781,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44515</v>
+        <v>46062</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10868,10 +10868,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45755</v>
+        <v>46062</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10941,10 +10941,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44887</v>
+        <v>44973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46154</v>
+        <v>44887</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11087,10 +11087,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45535</v>
+        <v>44963</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45931</v>
+        <v>46077</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46195</v>
+        <v>45180</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46195</v>
+        <v>44523</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45747</v>
+        <v>45028</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45350</v>
+        <v>46195</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11511,7 +11511,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45327</v>
+        <v>45123</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11584,7 +11584,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11598,10 +11598,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44546</v>
+        <v>46195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11613,13 +11613,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11662,7 +11657,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11672,14 +11667,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45523</v>
+        <v>45394</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11692,7 +11687,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11735,7 +11730,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11749,10 +11744,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45091</v>
+        <v>45196</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11808,7 +11803,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11822,10 +11817,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45028</v>
+        <v>45328</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11838,7 +11833,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11881,7 +11876,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11895,10 +11890,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45054</v>
+        <v>44656</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11911,7 +11906,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11954,7 +11949,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11968,10 +11963,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44858</v>
+        <v>44585</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11984,7 +11979,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12027,7 +12022,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12041,10 +12036,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45559</v>
+        <v>45189</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12057,7 +12052,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8.4</v>
+        <v>0.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12100,7 +12095,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12114,10 +12109,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44973</v>
+        <v>45350</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12130,7 +12125,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12173,7 +12168,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12187,10 +12182,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44802</v>
+        <v>45603</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12203,7 +12198,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12246,7 +12241,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12260,10 +12255,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45306</v>
+        <v>45327</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12276,7 +12271,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12319,7 +12314,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12333,10 +12328,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45306</v>
+        <v>44546</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12348,8 +12343,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12392,7 +12392,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12402,14 +12402,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45394</v>
+        <v>45054</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45180</v>
+        <v>45523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12538,7 +12538,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12548,14 +12548,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44636</v>
+        <v>45306</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12611,7 +12611,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12625,10 +12625,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44805</v>
+        <v>44967</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12684,7 +12684,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44949</v>
+        <v>44510</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12757,7 +12757,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12771,10 +12771,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45744</v>
+        <v>45747</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45596</v>
+        <v>45790</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12903,7 +12903,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12917,10 +12917,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45524</v>
+        <v>45329</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12976,7 +12976,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44656</v>
+        <v>45043</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13063,10 +13063,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45328</v>
+        <v>45257</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.1</v>
+        <v>2.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13122,7 +13122,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13136,10 +13136,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44963</v>
+        <v>45737</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44585</v>
+        <v>45833</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13282,10 +13282,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45329</v>
+        <v>45833</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45790</v>
+        <v>45833</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13431,7 +13431,7 @@
         <v>44713</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45894</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15890-2026</t>
+          <t>A 7903-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46107</v>
+        <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -1524,12 +1524,128 @@
         <v>8</v>
       </c>
       <c r="T9" t="n">
+        <v>20</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Björksplintborre
+Guldlockmossa
+Platt fjädermossa
+Spillkråka
+Kungsfågel
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15890-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
         <v>10</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>10</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -1541,152 +1657,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7903-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45350</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>20</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Björksplintborre
-Guldlockmossa
-Platt fjädermossa
-Spillkråka
-Kungsfågel
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32151-2026</t>
+          <t>A 24162-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46235</v>
+        <v>45796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2102,12 +2102,127 @@
         <v>7</v>
       </c>
       <c r="T14" t="n">
+        <v>19</v>
+      </c>
+      <c r="U14" t="n">
+        <v>19</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Blanksvart trämyra
+Blåmossa
+Spillkråka
+Kungsfågel
+Trana
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 32151-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
         <v>11</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>8</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Talltita
@@ -2118,158 +2233,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 24162-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45796</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>19</v>
-      </c>
-      <c r="U15" t="n">
-        <v>19</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Blanksvart trämyra
-Blåmossa
-Spillkråka
-Kungsfågel
-Trana
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26491-2024</t>
+          <t>A 63575-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45469</v>
+        <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,125 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Stor revmossa
+Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26491-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Gulpudrad spiklav
@@ -2346,111 +2459,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 12084-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45728</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka
@@ -2459,149 +2572,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 63575-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Stor revmossa
-Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58954-2022</t>
+          <t>A 11516-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,236 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes
+Vildkaprifol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33802-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik
+Björksplintborre
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 58954-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44903</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>9</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Blåmossa
@@ -2797,260 +3021,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11516-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes
-Vildkaprifol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33802-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik
-Björksplintborre
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>45930</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45123</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45540</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13306-2026</t>
+          <t>A 1503-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46094</v>
+        <v>45306</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -3566,1029 +3566,1029 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 16534-2025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 20586-2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45057</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 380-2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45662</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 13306-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Åkergroda</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 63569-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45275</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>2.4</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U33" t="n">
         <v>4</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 3413-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>44949</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>2.3</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U34" t="n">
         <v>3</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda
 Revlummer</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 12982-2024</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45385</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>3.3</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U35" t="n">
         <v>1</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Orre
 Revlummer</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>A 13380-2025</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D36" s="1" t="n">
         <v>45735</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E36" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
         <v>1.8</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>2</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T36" t="n">
         <v>5</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U36" t="n">
         <v>5</v>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE36">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 16534-2025</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45751</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 20586-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45057</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A 380-2025</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>45662</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2</v>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
         <v/>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
         <v>45595</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45394</v>
+        <v>45810</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4840,13 +4840,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4876,50 +4876,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4933,10 +4929,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45954</v>
+        <v>45331</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4949,13 +4945,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4989,46 +4985,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5042,10 +5034,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44564</v>
+        <v>45737</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5058,7 +5050,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5094,50 +5086,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5151,10 +5139,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46007</v>
+        <v>45954</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5167,7 +5155,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5207,42 +5195,46 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5256,10 +5248,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45712</v>
+        <v>46072</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5272,7 +5264,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5308,46 +5300,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5361,10 +5353,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46072</v>
+        <v>46007</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5377,7 +5369,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5413,46 +5405,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5466,10 +5458,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44827</v>
+        <v>45712</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5482,7 +5474,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5518,46 +5510,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5567,14 +5559,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45469</v>
+        <v>44564</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5587,7 +5579,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5620,49 +5612,53 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5672,14 +5668,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46245</v>
+        <v>45325</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,13 +5688,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5732,42 +5728,46 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45325</v>
+        <v>45469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -5830,53 +5830,49 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
-        <v/>
-      </c>
-      <c r="AE48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5890,10 +5886,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45518</v>
+        <v>45394</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5906,10 +5902,10 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -5918,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -5930,10 +5926,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5942,46 +5938,50 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <v/>
+      </c>
+      <c r="AE49">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45810</v>
+        <v>46245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6055,38 +6055,38 @@
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45331</v>
+        <v>45518</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6116,20 +6116,20 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>1</v>
       </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -6140,10 +6140,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6152,46 +6152,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45737</v>
+        <v>44827</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6257,39 +6257,39 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
         <v>45011</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44504</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44456</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 53144-2021</t>
+          <t>A 15508-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44468</v>
+        <v>44662</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6912,7 +6912,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20285-2022</t>
+          <t>A 53144-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6926,10 +6926,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44698</v>
+        <v>44468</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15508-2022</t>
+          <t>A 20285-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6999,10 +6999,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44662</v>
+        <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7058,7 +7058,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45091</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45307</v>
+        <v>44967</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7204,7 +7204,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45230</v>
+        <v>45307</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45744</v>
+        <v>44949</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7350,7 +7350,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44805</v>
+        <v>45308</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 49955-2021</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7437,10 +7437,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44456</v>
+        <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7496,7 +7496,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 49955-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7510,10 +7510,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44480</v>
+        <v>44456</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7583,10 +7583,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44963</v>
+        <v>45230</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7642,7 +7642,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44949</v>
+        <v>44475</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7715,7 +7715,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7729,10 +7729,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45222</v>
+        <v>45603</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7788,7 +7788,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7802,10 +7802,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45535</v>
+        <v>45043</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7861,7 +7861,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44475</v>
+        <v>45257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7934,7 +7934,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7948,10 +7948,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46118</v>
+        <v>44480</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8007,7 +8007,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45924</v>
+        <v>45737</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8080,7 +8080,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8094,10 +8094,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45524</v>
+        <v>44727</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>10</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8153,7 +8153,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8167,10 +8167,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44727</v>
+        <v>45833</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>10</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44896</v>
+        <v>45833</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8299,7 +8299,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8313,10 +8313,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44573</v>
+        <v>45833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8386,10 +8386,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44638</v>
+        <v>45123</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45559</v>
+        <v>46036</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46134</v>
+        <v>45222</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8591,7 +8591,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45943</v>
+        <v>45924</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45947</v>
+        <v>44573</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8737,7 +8737,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44662</v>
+        <v>44638</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8810,7 +8810,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45952</v>
+        <v>44896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8893,14 +8893,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45804</v>
+        <v>45943</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8956,7 +8956,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45091</v>
+        <v>45947</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.6</v>
+        <v>12</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9043,10 +9043,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46008</v>
+        <v>45091</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9102,7 +9102,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9116,10 +9116,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45894</v>
+        <v>45952</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45978</v>
+        <v>45196</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9248,7 +9248,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44802</v>
+        <v>46056</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9335,10 +9335,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45833</v>
+        <v>46058</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9394,7 +9394,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9408,10 +9408,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45308</v>
+        <v>46062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9467,7 +9467,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9481,10 +9481,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45989</v>
+        <v>46062</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9554,10 +9554,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44949</v>
+        <v>46062</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9613,7 +9613,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45994</v>
+        <v>44963</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9686,7 +9686,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44515</v>
+        <v>45978</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9759,7 +9759,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9769,14 +9769,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44636</v>
+        <v>44510</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.2</v>
+        <v>5.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9832,7 +9832,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45755</v>
+        <v>46077</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9919,10 +9919,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46002</v>
+        <v>45833</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9978,7 +9978,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9992,10 +9992,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46002</v>
+        <v>45989</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.9</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10051,7 +10051,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46154</v>
+        <v>44523</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44858</v>
+        <v>45994</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10197,7 +10197,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10211,10 +10211,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44585</v>
+        <v>46002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10270,7 +10270,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10284,10 +10284,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46036</v>
+        <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10343,7 +10343,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10357,10 +10357,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45306</v>
+        <v>44585</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10416,7 +10416,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10430,10 +10430,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45596</v>
+        <v>44515</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10489,7 +10489,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10503,10 +10503,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45931</v>
+        <v>45755</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10562,7 +10562,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10576,10 +10576,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46056</v>
+        <v>44887</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10649,10 +10649,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46058</v>
+        <v>46118</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.2</v>
+        <v>3.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10722,10 +10722,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46062</v>
+        <v>45535</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10781,7 +10781,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46062</v>
+        <v>45747</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10868,10 +10868,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46062</v>
+        <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10941,10 +10941,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44973</v>
+        <v>46134</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44887</v>
+        <v>45327</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11087,10 +11087,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44963</v>
+        <v>44546</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11102,8 +11102,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11146,7 +11151,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11160,10 +11165,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46077</v>
+        <v>45091</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11176,7 +11181,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11219,7 +11224,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11233,10 +11238,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45180</v>
+        <v>45028</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11249,7 +11254,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11292,7 +11297,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44523</v>
+        <v>45894</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11322,7 +11327,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11365,7 +11370,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11379,10 +11384,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45028</v>
+        <v>46008</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11395,7 +11400,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11438,7 +11443,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11448,14 +11453,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46195</v>
+        <v>45804</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11468,7 +11473,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11511,7 +11516,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11525,10 +11530,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45123</v>
+        <v>45054</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11541,7 +11546,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11584,7 +11589,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11598,10 +11603,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46195</v>
+        <v>46154</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11614,7 +11619,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11657,7 +11662,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11667,14 +11672,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45394</v>
+        <v>44858</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11687,7 +11692,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11730,7 +11735,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11744,10 +11749,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45196</v>
+        <v>45559</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11760,7 +11765,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>8.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11803,7 +11808,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11817,10 +11822,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45328</v>
+        <v>44973</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11833,7 +11838,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>7.1</v>
+        <v>10.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11876,7 +11881,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11890,10 +11895,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44656</v>
+        <v>45931</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11906,7 +11911,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11949,7 +11954,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11963,10 +11968,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44585</v>
+        <v>44802</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11979,7 +11984,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12022,7 +12027,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12036,10 +12041,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45189</v>
+        <v>45306</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12052,7 +12057,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.1</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12095,7 +12100,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12109,10 +12114,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45350</v>
+        <v>45306</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12125,7 +12130,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12168,7 +12173,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12182,10 +12187,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45603</v>
+        <v>46195</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12198,7 +12203,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12241,7 +12246,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12255,10 +12260,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45327</v>
+        <v>46195</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12271,7 +12276,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12314,7 +12319,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12324,14 +12329,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44546</v>
+        <v>45394</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12343,13 +12348,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12392,7 +12392,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12406,10 +12406,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45054</v>
+        <v>45180</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12475,14 +12475,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45523</v>
+        <v>44636</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12538,7 +12538,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45306</v>
+        <v>45523</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12611,7 +12611,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12625,10 +12625,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44967</v>
+        <v>44805</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12684,7 +12684,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12698,10 +12698,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44510</v>
+        <v>44949</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12757,7 +12757,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12771,10 +12771,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45747</v>
+        <v>45744</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45790</v>
+        <v>45596</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12903,7 +12903,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12917,10 +12917,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45329</v>
+        <v>45524</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12976,7 +12976,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12990,10 +12990,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45043</v>
+        <v>44656</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13063,10 +13063,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45257</v>
+        <v>45328</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.7</v>
+        <v>7.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13122,7 +13122,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13136,10 +13136,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45737</v>
+        <v>44963</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45833</v>
+        <v>44585</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13282,10 +13282,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45833</v>
+        <v>45329</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45833</v>
+        <v>45790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13431,7 +13431,7 @@
         <v>44713</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45894</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE152"/>
+  <dimension ref="A1:AE149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24162-2025</t>
+          <t>A 32151-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45796</v>
+        <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2102,12 +2102,127 @@
         <v>7</v>
       </c>
       <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Talltita
+Blåmossa
+Västlig hakmossa
+Spillkråka
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 24162-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
         <v>19</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>19</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Blanksvart trämyra
@@ -2118,158 +2233,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 32151-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Talltita
-Blåmossa
-Västlig hakmossa
-Spillkråka
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63575-2023</t>
+          <t>A 26491-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45275</v>
+        <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,238 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Gulpudrad spiklav
+Rostfläck
+Sotlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 12084-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka
+Kungsfågel
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 63575-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
         <v>7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -2346,262 +2572,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26491-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45469</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Gulpudrad spiklav
-Rostfläck
-Sotlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 12084-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka
-Kungsfågel
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11516-2026</t>
+          <t>A 58954-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46083</v>
+        <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,124 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Blåmossa
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 11516-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>6</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes
@@ -2797,111 +2909,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 33802-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>5.8</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>11</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Kortskaftad ärgspik
 Björksplintborre
@@ -2909,172 +3021,60 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 58954-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44903</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>9</v>
-      </c>
-      <c r="U22" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Blåmossa
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 47330-2025</t>
+          <t>S 2406-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45930</v>
+        <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3120,124 +3120,12 @@
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Älg
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 47330-2025 artfynd.xlsx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 47330-2025 karta.png", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 47330-2025 georefererad karta.tif", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 47330-2025 FSC-klagomål.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 47330-2025 FSC-klagomål mail.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 47330-2025 tillsynsbegäran.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 47330-2025 tillsynsbegäran mail.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 47330-2025 prioriterade fågelarter.docx", "A 47330-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>S 2406-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45123</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Rödgul trumpetsvamp
 Stor revmossa
@@ -3245,265 +3133,371 @@
 Sångsvan</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/S 2406-2023 artfynd.xlsx", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/S 2406-2023 karta.png", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/S 2406-2023 georefererad karta.tif", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/S 2406-2023 FSC-klagomål.docx", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/S 2406-2023 FSC-klagomål mail.docx", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/S 2406-2023 tillsynsbegäran.docx", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/S 2406-2023 tillsynsbegäran mail.docx", "S 2406-2023")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/S 2406-2023 prioriterade fågelarter.docx", "S 2406-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 14048-2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>46099</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>1.5</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U24" t="n">
         <v>3</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 37461-2024</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>45540</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>1.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Gulnål
 Spillkråka</t>
         </is>
       </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 13306-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Åkergroda</t>
+        </is>
+      </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1503-2024</t>
+          <t>A 16534-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3517,10 +3511,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45306</v>
+        <v>45751</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,16 +3527,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3557,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3566,943 +3560,947 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 20586-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45057</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 380-2025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45662</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 63569-2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
         <v>4</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U30" t="n">
         <v>4</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 3413-2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 12982-2024</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Orre
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 1503-2024</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="D35" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 16534-2025</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45751</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 20586-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45057</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 380-2025</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45662</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 13306-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Åkergroda</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 63569-2023</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" t="n">
-        <v>4</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 3413-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>44949</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 12982-2024</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45385</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Orre
-Revlummer</t>
-        </is>
-      </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
         <v/>
       </c>
       <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13380-2025</t>
+          <t>S 4485-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45735</v>
+        <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4515,16 +4513,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4539,7 +4537,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4548,71 +4546,67 @@
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Entita
-Spillkråka</t>
+          <t>Guldlockmossa
+Trädporella</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/S 4485-2024 artfynd.xlsx", "S 4485-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/S 4485-2024 karta.png", "S 4485-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/S 4485-2024 georefererad karta.tif", "S 4485-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/S 4485-2024 FSC-klagomål.docx", "S 4485-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/S 4485-2024 FSC-klagomål mail.docx", "S 4485-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/S 4485-2024 tillsynsbegäran.docx", "S 4485-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/S 4485-2024 tillsynsbegäran mail.docx", "S 4485-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S 4485-2024</t>
+          <t>A 41607-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45595</v>
+        <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4625,13 +4619,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4655,53 +4649,56 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Guldlockmossa
-Trädporella</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/S 4485-2024 artfynd.xlsx", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/S 4485-2024 karta.png", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/S 4485-2024 georefererad karta.tif", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/S 4485-2024 FSC-klagomål.docx", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/S 4485-2024 FSC-klagomål mail.docx", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/S 4485-2024 tillsynsbegäran.docx", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/S 4485-2024 tillsynsbegäran mail.docx", "S 4485-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41607-2022</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4715,10 +4712,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44827</v>
+        <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4731,7 +4728,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4767,50 +4764,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4824,10 +4821,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45810</v>
+        <v>46072</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4840,13 +4837,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4880,42 +4877,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4929,10 +4926,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45331</v>
+        <v>45737</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4945,13 +4942,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4985,42 +4982,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5034,10 +5031,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45737</v>
+        <v>44564</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5050,7 +5047,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5086,46 +5083,50 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5139,10 +5140,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45954</v>
+        <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5155,7 +5156,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5191,50 +5192,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5244,14 +5241,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46072</v>
+        <v>45469</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5264,7 +5261,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5297,49 +5294,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5353,10 +5350,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46007</v>
+        <v>45954</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5369,7 +5366,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5409,42 +5406,46 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5458,10 +5459,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45712</v>
+        <v>45518</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5474,20 +5475,20 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -5498,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5510,46 +5511,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5563,10 +5564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44564</v>
+        <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5579,13 +5580,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5619,46 +5620,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5668,14 +5665,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45325</v>
+        <v>46007</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5688,7 +5685,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5724,50 +5721,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5777,14 +5770,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45469</v>
+        <v>45712</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5797,7 +5790,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -5830,49 +5823,49 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5882,14 +5875,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45394</v>
+        <v>45325</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5902,7 +5895,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -5938,50 +5931,50 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5995,10 +5988,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46245</v>
+        <v>45810</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6011,7 +6004,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6055,38 +6048,38 @@
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6100,10 +6093,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45518</v>
+        <v>45331</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6116,19 +6109,19 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -6140,10 +6133,10 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6152,63 +6145,63 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>S 1062-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44827</v>
+        <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6221,13 +6214,13 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
         <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -6254,66 +6247,66 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/S 1062-2023 artfynd.xlsx", "S 1062-2023")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/S 1062-2023 karta.png", "S 1062-2023")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/S 1062-2023 georefererad karta.tif", "S 1062-2023")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/S 1062-2023 FSC-klagomål.docx", "S 1062-2023")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/S 1062-2023 FSC-klagomål mail.docx", "S 1062-2023")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/S 1062-2023 tillsynsbegäran.docx", "S 1062-2023")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/S 1062-2023 tillsynsbegäran mail.docx", "S 1062-2023")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S 1062-2023</t>
+          <t>A 62855-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45011</v>
+        <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6326,13 +6319,13 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -6356,52 +6349,20 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>Guldlockmossa</t>
-        </is>
-      </c>
-      <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/S 1062-2023 artfynd.xlsx", "S 1062-2023")</f>
-        <v/>
-      </c>
-      <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/S 1062-2023 karta.png", "S 1062-2023")</f>
-        <v/>
-      </c>
-      <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/S 1062-2023 georefererad karta.tif", "S 1062-2023")</f>
-        <v/>
-      </c>
-      <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/S 1062-2023 FSC-klagomål.docx", "S 1062-2023")</f>
-        <v/>
-      </c>
-      <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/S 1062-2023 FSC-klagomål mail.docx", "S 1062-2023")</f>
-        <v/>
-      </c>
-      <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/S 1062-2023 tillsynsbegäran.docx", "S 1062-2023")</f>
-        <v/>
-      </c>
-      <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/S 1062-2023 tillsynsbegäran mail.docx", "S 1062-2023")</f>
-        <v/>
-      </c>
+      <c r="V53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62855-2021</t>
+          <t>A 67165-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6415,10 +6376,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44504</v>
+        <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6431,7 +6392,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6474,7 +6435,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 67165-2021</t>
+          <t>A 3179-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6488,10 +6449,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44523</v>
+        <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6504,7 +6465,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6547,7 +6508,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49955-2021</t>
+          <t>A 65222-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6561,10 +6522,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44456</v>
+        <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6577,7 +6538,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6620,7 +6581,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3179-2022</t>
+          <t>A 66893-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6634,10 +6595,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44582</v>
+        <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6650,7 +6611,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6693,7 +6654,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 65222-2021</t>
+          <t>A 15508-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6707,10 +6668,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44515</v>
+        <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6723,7 +6684,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6766,7 +6727,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 66893-2021</t>
+          <t>A 53144-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6780,10 +6741,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44522</v>
+        <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6796,7 +6757,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6839,7 +6800,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15508-2022</t>
+          <t>A 20285-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6853,10 +6814,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44662</v>
+        <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6869,7 +6830,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6912,7 +6873,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53144-2021</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6926,10 +6887,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44468</v>
+        <v>45230</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6942,7 +6903,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6985,7 +6946,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20285-2022</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6999,10 +6960,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44698</v>
+        <v>45091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7015,7 +6976,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7058,7 +7019,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7072,10 +7033,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>44805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7088,7 +7049,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.1</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7131,7 +7092,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7145,10 +7106,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44967</v>
+        <v>44480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7161,7 +7122,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7204,7 +7165,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7218,10 +7179,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45307</v>
+        <v>44963</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7234,7 +7195,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7277,7 +7238,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7294,7 +7255,7 @@
         <v>44949</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7307,7 +7268,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7350,7 +7311,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7364,10 +7325,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45308</v>
+        <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7380,7 +7341,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7423,7 +7384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7437,10 +7398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44662</v>
+        <v>45535</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7453,7 +7414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7496,7 +7457,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49955-2021</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7510,10 +7471,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44456</v>
+        <v>44475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7526,7 +7487,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7569,7 +7530,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7583,10 +7544,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45230</v>
+        <v>44727</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7599,7 +7560,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7642,7 +7603,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7656,10 +7617,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44475</v>
+        <v>45737</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7715,7 +7676,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7729,10 +7690,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45603</v>
+        <v>46077</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7745,7 +7706,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7788,7 +7749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7802,10 +7763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45043</v>
+        <v>45833</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7818,7 +7779,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7861,7 +7822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7875,10 +7836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45257</v>
+        <v>45833</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7891,7 +7852,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7934,7 +7895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7948,10 +7909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44480</v>
+        <v>45833</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7964,7 +7925,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8007,7 +7968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8021,10 +7982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45737</v>
+        <v>45091</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8037,7 +7998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8080,7 +8041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8094,10 +8055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44727</v>
+        <v>46118</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8110,7 +8071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8153,7 +8114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8167,10 +8128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45833</v>
+        <v>44802</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8183,7 +8144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8226,7 +8187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8240,10 +8201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45833</v>
+        <v>46134</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8256,7 +8217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8299,7 +8260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8313,10 +8274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45833</v>
+        <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8329,7 +8290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8372,7 +8333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8382,14 +8343,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45123</v>
+        <v>45804</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8402,7 +8363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8445,7 +8406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8459,10 +8420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46036</v>
+        <v>46008</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8475,7 +8436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8518,7 +8479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8532,10 +8493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45222</v>
+        <v>45894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8548,7 +8509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8591,7 +8552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8605,10 +8566,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45924</v>
+        <v>44858</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8621,7 +8582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8664,7 +8625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8678,10 +8639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44573</v>
+        <v>45924</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8694,7 +8655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8737,7 +8698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8751,10 +8712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44638</v>
+        <v>45306</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8767,7 +8728,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8810,7 +8771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8824,10 +8785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44896</v>
+        <v>45596</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8840,7 +8801,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8883,7 +8844,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8897,10 +8858,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45943</v>
+        <v>44896</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8913,7 +8874,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8956,7 +8917,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8970,10 +8931,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45947</v>
+        <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8986,7 +8947,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9029,7 +8990,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9043,10 +9004,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45091</v>
+        <v>44638</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9059,7 +9020,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9102,7 +9063,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9116,10 +9077,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45952</v>
+        <v>46154</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9132,7 +9093,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9175,7 +9136,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9189,10 +9150,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45196</v>
+        <v>44973</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9205,7 +9166,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9248,7 +9209,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9262,10 +9223,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46056</v>
+        <v>44887</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9278,7 +9239,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9321,7 +9282,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9335,10 +9296,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46058</v>
+        <v>45180</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9351,7 +9312,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9394,7 +9355,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9408,10 +9369,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46062</v>
+        <v>45943</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9424,7 +9385,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9467,7 +9428,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9481,10 +9442,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46062</v>
+        <v>44523</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9497,7 +9458,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9540,7 +9501,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9554,10 +9515,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46062</v>
+        <v>45028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9570,7 +9531,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9613,7 +9574,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9627,10 +9588,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44963</v>
+        <v>45123</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9643,7 +9604,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9686,7 +9647,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9696,14 +9657,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45978</v>
+        <v>45394</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9716,7 +9677,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9759,7 +9720,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9773,10 +9734,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44510</v>
+        <v>45931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9789,7 +9750,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9832,7 +9793,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9846,10 +9807,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46077</v>
+        <v>45947</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9862,7 +9823,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.8</v>
+        <v>12</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9905,7 +9866,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9919,10 +9880,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45833</v>
+        <v>45196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9935,7 +9896,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9978,7 +9939,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9992,10 +9953,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45989</v>
+        <v>45328</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10008,7 +9969,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10051,7 +10012,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10065,10 +10026,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44523</v>
+        <v>45952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10081,7 +10042,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10124,7 +10085,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10138,10 +10099,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45994</v>
+        <v>44656</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10154,7 +10115,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10197,7 +10158,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10211,10 +10172,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46002</v>
+        <v>44585</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10227,7 +10188,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10270,7 +10231,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10284,10 +10245,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46002</v>
+        <v>46195</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10300,7 +10261,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10343,7 +10304,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10357,10 +10318,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44585</v>
+        <v>46195</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10373,7 +10334,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10416,7 +10377,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10430,10 +10391,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44515</v>
+        <v>45189</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10446,7 +10407,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10489,7 +10450,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10503,10 +10464,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45755</v>
+        <v>45350</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10519,7 +10480,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10562,7 +10523,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10576,10 +10537,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44887</v>
+        <v>45603</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10592,7 +10553,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10635,7 +10596,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10649,10 +10610,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46118</v>
+        <v>45327</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10665,7 +10626,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10708,7 +10669,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10722,10 +10683,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45535</v>
+        <v>44546</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10737,8 +10698,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10781,7 +10747,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10795,10 +10761,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45747</v>
+        <v>45978</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10811,7 +10777,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10854,7 +10820,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10868,10 +10834,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45350</v>
+        <v>45307</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10884,7 +10850,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10927,7 +10893,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10941,10 +10907,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46134</v>
+        <v>45833</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10957,7 +10923,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11000,7 +10966,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11014,10 +10980,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45327</v>
+        <v>45744</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11030,7 +10996,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11073,7 +11039,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11087,10 +11053,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44546</v>
+        <v>45989</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11102,13 +11068,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11151,7 +11112,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11165,10 +11126,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45091</v>
+        <v>45994</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11181,7 +11142,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11224,7 +11185,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11238,10 +11199,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45028</v>
+        <v>45523</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11254,7 +11215,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11297,7 +11258,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11311,10 +11272,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45894</v>
+        <v>46002</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11327,7 +11288,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11370,7 +11331,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11384,10 +11345,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11400,7 +11361,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11443,7 +11404,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11453,14 +11414,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45804</v>
+        <v>45524</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11473,7 +11434,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11516,7 +11477,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11530,10 +11491,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45054</v>
+        <v>45559</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11546,7 +11507,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11589,7 +11550,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11603,10 +11564,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46154</v>
+        <v>44662</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11619,7 +11580,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11662,7 +11623,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11676,10 +11637,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44858</v>
+        <v>45308</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11692,7 +11653,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11735,7 +11696,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11749,10 +11710,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45559</v>
+        <v>44949</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11765,7 +11726,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11808,7 +11769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11822,10 +11783,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44973</v>
+        <v>44515</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11838,7 +11799,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>10.5</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11881,7 +11842,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11891,14 +11852,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45931</v>
+        <v>44636</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11911,7 +11872,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11954,7 +11915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11968,10 +11929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44802</v>
+        <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11984,7 +11945,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12027,7 +11988,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12041,10 +12002,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45306</v>
+        <v>44585</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12057,7 +12018,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12100,7 +12061,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12114,10 +12075,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45306</v>
+        <v>44963</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12130,7 +12091,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12173,7 +12134,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12187,10 +12148,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46195</v>
+        <v>46056</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12203,7 +12164,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12246,7 +12207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12260,10 +12221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46195</v>
+        <v>46058</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12276,7 +12237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>7.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12319,7 +12280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12329,14 +12290,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45394</v>
+        <v>46062</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12349,7 +12310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12392,7 +12353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12406,10 +12367,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45180</v>
+        <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12422,7 +12383,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12465,7 +12426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12475,14 +12436,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44636</v>
+        <v>46062</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12495,7 +12456,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12538,7 +12499,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12552,10 +12513,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45523</v>
+        <v>45054</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12568,7 +12529,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12611,7 +12572,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12625,10 +12586,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44805</v>
+        <v>45306</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12641,7 +12602,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12684,7 +12645,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12698,10 +12659,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44949</v>
+        <v>44967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12714,7 +12675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12757,7 +12718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12771,10 +12732,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45744</v>
+        <v>44510</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12787,7 +12748,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12830,7 +12791,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12844,10 +12805,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45596</v>
+        <v>45747</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12860,7 +12821,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12903,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12917,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45524</v>
+        <v>45790</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12933,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12976,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12990,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44656</v>
+        <v>45329</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13006,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13049,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13063,10 +13024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45328</v>
+        <v>45043</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13079,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.1</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13122,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13136,10 +13097,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44963</v>
+        <v>45257</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13152,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13195,24 +13156,24 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>S 2992-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44585</v>
+        <v>44713</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13225,7 +13186,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13268,24 +13229,24 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>S 4359-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45329</v>
+        <v>45587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13298,7 +13259,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13338,27 +13299,27 @@
       </c>
       <c r="V148" s="2" t="inlineStr"/>
     </row>
-    <row r="149" ht="15" customHeight="1">
+    <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>S 2388-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45790</v>
+        <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13371,7 +13332,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13410,225 +13371,6 @@
         <v>0</v>
       </c>
       <c r="V149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>S 2992-2022</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Åtgärd i nyckelbiotop</t>
-        </is>
-      </c>
-      <c r="D150" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="E150" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151" ht="15" customHeight="1">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>S 4359-2024</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D151" s="1" t="n">
-        <v>45587</v>
-      </c>
-      <c r="E151" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
-      <c r="R151" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" t="n">
-        <v>0</v>
-      </c>
-      <c r="V151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>S 2388-2025</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D152" s="1" t="n">
-        <v>45894</v>
-      </c>
-      <c r="E152" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I152" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" t="n">
-        <v>0</v>
-      </c>
-      <c r="T152" t="n">
-        <v>0</v>
-      </c>
-      <c r="U152" t="n">
-        <v>0</v>
-      </c>
-      <c r="V152" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 41294-2024</t>
+          <t>A 32849-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45559</v>
+        <v>45124</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1050,12 +1050,132 @@
         <v>12</v>
       </c>
       <c r="T5" t="n">
+        <v>41</v>
+      </c>
+      <c r="U5" t="n">
+        <v>41</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Motaggsvamp
+Blåmossa
+Kornknutmossa
+Sotriska
+Stor revmossa
+Stubbspretmossa
+Västlig hakmossa
+Spillkråka
+Kungsfågel
+Vanlig groda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32849-2023 artfynd.xlsx", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32849-2023 karta.png", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32849-2023 georefererad karta.tif", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32849-2023 FSC-klagomål.docx", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32849-2023 FSC-klagomål mail.docx", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32849-2023 tillsynsbegäran.docx", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32849-2023 tillsynsbegäran mail.docx", "A 32849-2023")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32849-2023 prioriterade fågelarter.docx", "A 32849-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 41294-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45559</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
         <v>23</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>23</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Björksplintborre
@@ -1071,156 +1191,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41294-2024 artfynd.xlsx", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41294-2024 karta.png", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41294-2024 georefererad karta.tif", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41294-2024 FSC-klagomål.docx", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41294-2024 FSC-klagomål mail.docx", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41294-2024 tillsynsbegäran.docx", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41294-2024 tillsynsbegäran mail.docx", "A 41294-2024")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41294-2024 prioriterade fågelarter.docx", "A 41294-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 32849-2023</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45124</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>41</v>
-      </c>
-      <c r="U6" t="n">
-        <v>41</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Motaggsvamp
-Blåmossa
-Kornknutmossa
-Sotriska
-Stor revmossa
-Stubbspretmossa
-Västlig hakmossa
-Spillkråka
-Kungsfågel
-Vanlig groda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32849-2023 artfynd.xlsx", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32849-2023 karta.png", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32849-2023 georefererad karta.tif", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32849-2023 FSC-klagomål.docx", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32849-2023 FSC-klagomål mail.docx", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32849-2023 tillsynsbegäran.docx", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32849-2023 tillsynsbegäran mail.docx", "A 32849-2023")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32849-2023 prioriterade fågelarter.docx", "A 32849-2023")</f>
         <v/>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32151-2026</t>
+          <t>A 24162-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46235</v>
+        <v>45796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2102,12 +2102,127 @@
         <v>7</v>
       </c>
       <c r="T14" t="n">
+        <v>19</v>
+      </c>
+      <c r="U14" t="n">
+        <v>19</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Blanksvart trämyra
+Blåmossa
+Spillkråka
+Kungsfågel
+Trana
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 32151-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
         <v>11</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>8</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Talltita
@@ -2118,158 +2233,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 24162-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45796</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>19</v>
-      </c>
-      <c r="U15" t="n">
-        <v>19</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Blanksvart trämyra
-Blåmossa
-Spillkråka
-Kungsfågel
-Trana
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26491-2024</t>
+          <t>A 63575-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45469</v>
+        <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,125 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Stor revmossa
+Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26491-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Gulpudrad spiklav
@@ -2346,111 +2459,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 12084-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45728</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka
@@ -2459,149 +2572,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 63575-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Stor revmossa
-Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58954-2022</t>
+          <t>A 11516-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,236 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes
+Vildkaprifol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33802-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik
+Björksplintborre
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 58954-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44903</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>9</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Blåmossa
@@ -2797,260 +3021,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11516-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes
-Vildkaprifol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33802-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik
-Björksplintborre
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>46099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45540</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13306-2026</t>
+          <t>A 63569-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46094</v>
+        <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>9.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3454,1029 +3454,1029 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 3413-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 13306-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Åkergroda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 12982-2024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Orre
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 1503-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 16534-2025</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45751</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>1.5</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 20586-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>45057</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>1.5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U34" t="n">
         <v>3</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 380-2025</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45662</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>8.6</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U35" t="n">
         <v>2</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 63569-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>4</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 13380-2025</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45735</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>5</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 3413-2023</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>44949</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 12982-2024</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45385</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Orre
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
         <v/>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45394</v>
+        <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4764,50 +4764,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46072</v>
+        <v>45954</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4873,46 +4873,50 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4922,14 +4926,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45737</v>
+        <v>45325</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4942,7 +4946,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4978,46 +4982,50 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5031,10 +5039,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44564</v>
+        <v>46007</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5047,7 +5055,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5083,50 +5091,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5140,10 +5144,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44827</v>
+        <v>45712</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5156,7 +5160,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>5.7</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5192,39 +5196,39 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
@@ -5248,7 +5252,7 @@
         <v>45469</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5336,7 +5340,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5350,10 +5354,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45954</v>
+        <v>46072</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5366,7 +5370,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5402,50 +5406,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45518</v>
+        <v>45394</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5487,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5499,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5511,39 +5511,43 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
@@ -5567,7 +5571,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5655,7 +5659,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5669,10 +5673,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46007</v>
+        <v>45518</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,20 +5689,20 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
@@ -5709,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5721,46 +5725,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5774,10 +5778,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45712</v>
+        <v>44827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,7 +5794,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -5826,46 +5830,46 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5875,14 +5879,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45325</v>
+        <v>45810</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,13 +5899,13 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5935,46 +5939,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
-        <v/>
-      </c>
-      <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45810</v>
+        <v>45331</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6040,46 +6040,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45331</v>
+        <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -6149,35 +6149,35 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45230</v>
+        <v>44967</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45091</v>
+        <v>45307</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44805</v>
+        <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>0.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44480</v>
+        <v>44949</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44963</v>
+        <v>44662</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44949</v>
+        <v>45308</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45222</v>
+        <v>45230</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45535</v>
+        <v>45603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>44475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44727</v>
+        <v>44480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45737</v>
+        <v>44727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46077</v>
+        <v>45123</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45833</v>
+        <v>45222</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45833</v>
+        <v>45091</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45833</v>
+        <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45091</v>
+        <v>44963</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46118</v>
+        <v>44510</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44802</v>
+        <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46134</v>
+        <v>45894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45755</v>
+        <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8343,14 +8343,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45804</v>
+        <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46008</v>
+        <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45894</v>
+        <v>45924</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44858</v>
+        <v>45804</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45924</v>
+        <v>44573</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45306</v>
+        <v>44638</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45596</v>
+        <v>44896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44896</v>
+        <v>45755</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44573</v>
+        <v>44887</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44638</v>
+        <v>45943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46154</v>
+        <v>45535</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44973</v>
+        <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44887</v>
+        <v>45952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45180</v>
+        <v>45747</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45943</v>
+        <v>45350</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44523</v>
+        <v>45327</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45028</v>
+        <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9530,8 +9530,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9574,7 +9579,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9588,10 +9593,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45123</v>
+        <v>46154</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9604,7 +9609,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9647,7 +9652,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9657,14 +9662,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45394</v>
+        <v>45091</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9682,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9720,7 +9725,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9734,10 +9739,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45931</v>
+        <v>45978</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9750,7 +9755,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9793,7 +9798,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9807,10 +9812,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45947</v>
+        <v>45833</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9823,7 +9828,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>12</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9866,7 +9871,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9880,10 +9885,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45196</v>
+        <v>45989</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9896,7 +9901,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9939,7 +9944,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9953,10 +9958,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45328</v>
+        <v>45028</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9969,7 +9974,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10012,7 +10017,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10026,10 +10031,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45952</v>
+        <v>45994</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10042,7 +10047,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10085,7 +10090,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10099,10 +10104,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44656</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10115,7 +10120,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10158,7 +10163,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10172,10 +10177,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44585</v>
+        <v>45054</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10188,7 +10193,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10231,7 +10236,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10245,10 +10250,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46195</v>
+        <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10261,7 +10266,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10304,7 +10309,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10318,10 +10323,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46195</v>
+        <v>44858</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10334,7 +10339,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10377,7 +10382,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10391,10 +10396,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45189</v>
+        <v>45559</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10407,7 +10412,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.1</v>
+        <v>8.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10450,7 +10455,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10464,10 +10469,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45350</v>
+        <v>46036</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10480,7 +10485,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10523,7 +10528,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10537,10 +10542,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45603</v>
+        <v>44973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10553,7 +10558,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10596,7 +10601,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10610,10 +10615,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45327</v>
+        <v>46056</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10626,7 +10631,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10669,7 +10674,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10683,10 +10688,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44546</v>
+        <v>45931</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10698,13 +10703,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10747,7 +10747,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45978</v>
+        <v>46058</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45307</v>
+        <v>46062</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10893,7 +10893,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45833</v>
+        <v>46062</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45744</v>
+        <v>46062</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11039,7 +11039,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11053,10 +11053,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45989</v>
+        <v>46077</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11126,10 +11126,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45994</v>
+        <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11185,7 +11185,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45523</v>
+        <v>45306</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11258,7 +11258,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11272,10 +11272,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>45306</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46002</v>
+        <v>46195</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11404,7 +11404,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45524</v>
+        <v>46195</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11487,14 +11487,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45559</v>
+        <v>45394</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11564,10 +11564,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44662</v>
+        <v>46118</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11623,7 +11623,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11637,10 +11637,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45308</v>
+        <v>45180</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11696,7 +11696,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44949</v>
+        <v>46134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11769,7 +11769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11779,14 +11779,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44515</v>
+        <v>44636</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11852,14 +11852,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44636</v>
+        <v>44805</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11915,7 +11915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46036</v>
+        <v>44949</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12002,10 +12002,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44585</v>
+        <v>45744</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44963</v>
+        <v>45596</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46056</v>
+        <v>45524</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46058</v>
+        <v>44656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.2</v>
+        <v>1.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46062</v>
+        <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46062</v>
+        <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12426,7 +12426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46062</v>
+        <v>44963</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45054</v>
+        <v>44585</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45306</v>
+        <v>45329</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12645,7 +12645,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12659,10 +12659,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44967</v>
+        <v>45790</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44510</v>
+        <v>45043</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45747</v>
+        <v>45257</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45790</v>
+        <v>45737</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45329</v>
+        <v>45833</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45043</v>
+        <v>45833</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13083,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45257</v>
+        <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13173,7 +13173,7 @@
         <v>44713</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
         <v>27</v>
       </c>
       <c r="T3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="U3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45124</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45559</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45796</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>46235</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45469</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>46251</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>44903</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>46099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45540</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44949</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>46094</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45385</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45735</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45306</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45662</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45954</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>45325</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>46007</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>45712</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45469</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46072</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>45394</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>46245</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45518</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44827</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45810</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45331</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>44967</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45307</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>45189</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44949</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44662</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45308</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45230</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44475</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45123</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45222</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45091</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44963</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44510</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>45894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46008</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45924</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45804</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>44573</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>44638</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>45755</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44887</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45943</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45535</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45952</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45747</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45350</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45327</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44546</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>46154</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45091</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45978</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45833</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>45989</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45028</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>45994</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45054</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>46002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>44858</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45559</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>46036</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>46056</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45931</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>46058</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>46062</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>46062</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>46062</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>46077</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44802</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45306</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45306</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>46195</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>46195</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45394</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>46118</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45180</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>46134</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44636</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44805</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44949</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45744</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45596</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>45524</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>44656</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44963</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44585</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45329</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45790</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45043</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45257</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45737</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45833</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>45833</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>44713</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE149"/>
+  <dimension ref="A1:AE150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 32849-2023</t>
+          <t>A 41294-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45124</v>
+        <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1050,12 +1050,132 @@
         <v>12</v>
       </c>
       <c r="T5" t="n">
+        <v>23</v>
+      </c>
+      <c r="U5" t="n">
+        <v>23</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Björksplintborre
+Grönpyrola
+Kornknutmossa
+Smal svampklubba
+Stor revmossa
+Västlig hakmossa
+Spillkråka
+Tjäder
+Grönsiska
+Kungsfågel
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41294-2024 artfynd.xlsx", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41294-2024 karta.png", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41294-2024 georefererad karta.tif", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41294-2024 FSC-klagomål.docx", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41294-2024 FSC-klagomål mail.docx", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41294-2024 tillsynsbegäran.docx", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41294-2024 tillsynsbegäran mail.docx", "A 41294-2024")</f>
+        <v/>
+      </c>
+      <c r="AE5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41294-2024 prioriterade fågelarter.docx", "A 41294-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 32849-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45124</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="n">
         <v>41</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>41</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Motaggsvamp
@@ -1071,156 +1191,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32849-2023 artfynd.xlsx", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32849-2023 karta.png", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32849-2023 georefererad karta.tif", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32849-2023 FSC-klagomål.docx", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32849-2023 FSC-klagomål mail.docx", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32849-2023 tillsynsbegäran.docx", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32849-2023 tillsynsbegäran mail.docx", "A 32849-2023")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32849-2023 prioriterade fågelarter.docx", "A 32849-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 41294-2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45559</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>23</v>
-      </c>
-      <c r="U6" t="n">
-        <v>23</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Björksplintborre
-Grönpyrola
-Kornknutmossa
-Smal svampklubba
-Stor revmossa
-Västlig hakmossa
-Spillkråka
-Tjäder
-Grönsiska
-Kungsfågel
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41294-2024 artfynd.xlsx", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41294-2024 karta.png", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41294-2024 georefererad karta.tif", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41294-2024 FSC-klagomål.docx", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41294-2024 FSC-klagomål mail.docx", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41294-2024 tillsynsbegäran.docx", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41294-2024 tillsynsbegäran mail.docx", "A 41294-2024")</f>
-        <v/>
-      </c>
-      <c r="AE6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41294-2024 prioriterade fågelarter.docx", "A 41294-2024")</f>
         <v/>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 24162-2025</t>
+          <t>A 32151-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45796</v>
+        <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
         <v>5</v>
@@ -2078,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2102,12 +2102,127 @@
         <v>7</v>
       </c>
       <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Talltita
+Blåmossa
+Västlig hakmossa
+Spillkråka
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 24162-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
         <v>19</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>19</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Blanksvart trämyra
@@ -2118,151 +2233,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 32151-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Talltita
-Blåmossa
-Västlig hakmossa
-Spillkråka
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
         <v/>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
         <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45469</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>46251</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>44903</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>46099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45540</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3413-2023</t>
+          <t>A 13306-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44949</v>
+        <v>46094</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -3564,149 +3564,149 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Åkergroda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 3413-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
         <v>3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>3</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda
 Revlummer</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 13306-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Åkergroda</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
         <v>45385</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45735</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45306</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>45673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>45751</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45057</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45662</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44564</v>
+        <v>45954</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4764,50 +4764,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45954</v>
+        <v>44564</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4873,50 +4873,50 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4926,14 +4926,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45325</v>
+        <v>46007</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4982,50 +4982,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5039,10 +5035,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46007</v>
+        <v>45712</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5055,7 +5051,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5095,42 +5091,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5140,14 +5136,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45712</v>
+        <v>45325</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5160,7 +5156,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5196,46 +5192,50 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5245,14 +5245,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45469</v>
+        <v>46072</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5298,49 +5298,49 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5350,14 +5350,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46072</v>
+        <v>45469</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5403,42 +5403,42 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
         <v>45394</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46245</v>
+        <v>45518</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5584,20 +5584,20 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>1</v>
       </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
@@ -5608,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5624,42 +5624,42 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5673,10 +5673,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45518</v>
+        <v>44827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5729,42 +5729,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44827</v>
+        <v>46245</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5794,13 +5794,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5834,35 +5834,35 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
         <v>45810</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>45331</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44967</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45307</v>
+        <v>44967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45189</v>
+        <v>45307</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>44949</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44662</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45308</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45230</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45603</v>
+        <v>44475</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44475</v>
+        <v>45603</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
         <v>44480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45123</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45222</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45091</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44963</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44510</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44523</v>
+        <v>45924</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45894</v>
+        <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46008</v>
+        <v>45894</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44585</v>
+        <v>46008</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44515</v>
+        <v>44573</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45924</v>
+        <v>44638</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8562,14 +8562,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45804</v>
+        <v>44896</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8635,14 +8635,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44573</v>
+        <v>45804</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44638</v>
+        <v>45943</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44896</v>
+        <v>46154</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45755</v>
+        <v>45947</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44887</v>
+        <v>44585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45943</v>
+        <v>44515</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45535</v>
+        <v>45952</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45947</v>
+        <v>45755</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45952</v>
+        <v>44887</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45747</v>
+        <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.2</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45350</v>
+        <v>45535</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45327</v>
+        <v>45833</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44546</v>
+        <v>45989</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9530,13 +9530,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9579,7 +9574,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9593,10 +9588,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46154</v>
+        <v>45747</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9609,7 +9604,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9652,7 +9647,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9666,10 +9661,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45091</v>
+        <v>45350</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9682,7 +9677,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9725,7 +9720,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9739,10 +9734,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9755,7 +9750,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9798,7 +9793,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9812,10 +9807,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45833</v>
+        <v>46002</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9828,7 +9823,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9871,7 +9866,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9885,10 +9880,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45989</v>
+        <v>46002</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9901,7 +9896,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9944,7 +9939,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9958,10 +9953,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45028</v>
+        <v>45327</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9974,7 +9969,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10017,7 +10012,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10031,10 +10026,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45994</v>
+        <v>44546</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10046,8 +10041,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10090,7 +10090,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>45931</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45054</v>
+        <v>45091</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10236,7 +10236,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46002</v>
+        <v>46036</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10309,7 +10309,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44858</v>
+        <v>45028</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45559</v>
+        <v>46195</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10469,10 +10469,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46036</v>
+        <v>46056</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44973</v>
+        <v>46195</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45931</v>
+        <v>46062</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10747,7 +10747,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.2</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10837,7 +10837,7 @@
         <v>46062</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10893,7 +10893,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46062</v>
+        <v>45054</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46062</v>
+        <v>46077</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11039,7 +11039,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11053,10 +11053,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46077</v>
+        <v>44858</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11126,10 +11126,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44802</v>
+        <v>45559</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11185,7 +11185,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45306</v>
+        <v>44973</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>10.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11258,7 +11258,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11272,10 +11272,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45306</v>
+        <v>46118</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46195</v>
+        <v>46134</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11404,7 +11404,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46195</v>
+        <v>44802</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11487,14 +11487,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45394</v>
+        <v>45306</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11564,10 +11564,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46118</v>
+        <v>45306</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11623,7 +11623,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11637,10 +11637,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45180</v>
+        <v>45523</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11696,7 +11696,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11706,14 +11706,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46134</v>
+        <v>45394</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11769,7 +11769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11779,14 +11779,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44636</v>
+        <v>45180</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11852,14 +11852,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44805</v>
+        <v>44636</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.1</v>
+        <v>0.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11915,7 +11915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44949</v>
+        <v>44805</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12002,10 +12002,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45744</v>
+        <v>44949</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45596</v>
+        <v>45744</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45524</v>
+        <v>45596</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44656</v>
+        <v>45524</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45328</v>
+        <v>44656</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45523</v>
+        <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.2</v>
+        <v>7.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12426,7 +12426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 38843-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44963</v>
+        <v>46286</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44585</v>
+        <v>44963</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45329</v>
+        <v>44585</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12645,7 +12645,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12659,10 +12659,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45790</v>
+        <v>45329</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45043</v>
+        <v>45790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45257</v>
+        <v>45043</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45737</v>
+        <v>45257</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45833</v>
+        <v>45737</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13027,7 +13027,7 @@
         <v>45833</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13083,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13100,7 +13100,7 @@
         <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13156,24 +13156,24 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>S 2992-2022</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44713</v>
+        <v>45833</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13229,148 +13229,221 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
+          <t>S 2992-2022</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Åtgärd i nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="E148" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149" ht="15" customHeight="1">
+      <c r="A149" t="inlineStr">
+        <is>
           <t>S 4359-2024</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D148" s="1" t="n">
+      <c r="D149" s="1" t="n">
         <v>45587</v>
       </c>
-      <c r="E148" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I148" t="n">
+      <c r="E149" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
         <v>1.8</v>
       </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>S 2388-2025</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D149" s="1" t="n">
+      <c r="D150" s="1" t="n">
         <v>45894</v>
       </c>
-      <c r="E149" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
+      <c r="E150" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
         <v>7.4</v>
       </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" s="2" t="inlineStr"/>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE150"/>
+  <dimension ref="A1:AE151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 40059-2025</t>
+          <t>A 15890-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45894</v>
+        <v>46107</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.9</v>
+        <v>6.1</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
@@ -1408,12 +1408,128 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Björksplintborre
+Spillkråka
+Späd frullania
+Kungsfågel
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 40059-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
         <v>9</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>9</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Gropticka
 Talltita
@@ -1425,111 +1541,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 40059-2025 artfynd.xlsx", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 40059-2025 karta.png", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 40059-2025 georefererad karta.tif", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 40059-2025 FSC-klagomål.docx", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 40059-2025 FSC-klagomål mail.docx", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 40059-2025 tillsynsbegäran.docx", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 40059-2025 tillsynsbegäran mail.docx", "A 40059-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 40059-2025 prioriterade fågelarter.docx", "A 40059-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 7903-2024</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>45350</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>4.2</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>8</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>20</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>20</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita
@@ -1541,152 +1657,36 @@
 Vanlig snok</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 15890-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>10</v>
-      </c>
-      <c r="U10" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Björksplintborre
-Spillkråka
-Späd frullania
-Kungsfågel
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 17684-2026</t>
+          <t>A 24162-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46121</v>
+        <v>45796</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,16 +1839,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1872,12 +1872,127 @@
         <v>7</v>
       </c>
       <c r="T12" t="n">
+        <v>19</v>
+      </c>
+      <c r="U12" t="n">
+        <v>19</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Blanksvart trämyra
+Blåmossa
+Spillkråka
+Kungsfågel
+Trana
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 17684-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Bronshjon
@@ -1888,111 +2003,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 17684-2026 artfynd.xlsx", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 17684-2026 karta.png", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 17684-2026 georefererad karta.tif", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 17684-2026 FSC-klagomål.docx", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 17684-2026 FSC-klagomål mail.docx", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 17684-2026 tillsynsbegäran.docx", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 17684-2026 tillsynsbegäran mail.docx", "A 17684-2026")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 17684-2026 prioriterade fågelarter.docx", "A 17684-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 60293-2025</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45994</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>1.9</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>7</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>10</v>
       </c>
-      <c r="U13" t="n">
+      <c r="U14" t="n">
         <v>10</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Entita
 Rödvingetrast
@@ -2003,111 +2118,111 @@
 Stjärtmes</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 60293-2025 artfynd.xlsx", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 60293-2025 karta.png", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 60293-2025 georefererad karta.tif", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 60293-2025 FSC-klagomål.docx", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 60293-2025 FSC-klagomål mail.docx", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 60293-2025 tillsynsbegäran.docx", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 60293-2025 tillsynsbegäran mail.docx", "A 60293-2025")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 60293-2025 prioriterade fågelarter.docx", "A 60293-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 32151-2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>4.9</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>7</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>11</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>8</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Mindre hackspett
 Talltita
@@ -2118,158 +2233,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 24162-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45796</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>19</v>
-      </c>
-      <c r="U15" t="n">
-        <v>19</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Blanksvart trämyra
-Blåmossa
-Spillkråka
-Kungsfågel
-Trana
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63575-2023</t>
+          <t>A 26491-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45275</v>
+        <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,125 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Gulpudrad spiklav
+Rostfläck
+Sotlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 63575-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -2346,149 +2459,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26491-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45469</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Gulpudrad spiklav
-Rostfläck
-Sotlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
         <v/>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>45728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11516-2026</t>
+          <t>A 58954-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46083</v>
+        <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,124 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Blåmossa
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 11516-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>6</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes
@@ -2797,111 +2909,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 33802-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>5.8</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>11</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Kortskaftad ärgspik
 Björksplintborre
@@ -2909,148 +3021,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 58954-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44903</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>9</v>
-      </c>
-      <c r="U22" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Blåmossa
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14048-2026</t>
+          <t>A 37461-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46099</v>
+        <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3235,163 +3235,163 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Gulnål
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 14048-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 37461-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Gulnål
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63569-2023</t>
+          <t>A 2270-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45275</v>
+        <v>45673</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3454,1029 +3454,1029 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 1503-2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>4</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 3413-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 13306-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Åkergroda</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 12982-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Orre
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 16534-2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 20586-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45057</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A 380-2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45662</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="X34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A 63569-2023</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 13306-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Åkergroda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 3413-2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>44949</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>3</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 12982-2024</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45385</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Orre
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 13380-2025</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45735</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>4</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 16534-2025</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45751</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 20586-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45057</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 380-2025</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45662</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
         <v/>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41607-2022</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44827</v>
+        <v>44564</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>6.8</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4663,42 +4663,42 @@
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 41607-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45954</v>
+        <v>44827</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4764,50 +4764,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44564</v>
+        <v>45394</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4873,50 +4873,50 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46007</v>
+        <v>44827</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4982,46 +4982,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45712</v>
+        <v>45810</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5087,46 +5087,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45325</v>
+        <v>45469</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5189,53 +5189,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5249,10 +5245,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46072</v>
+        <v>45331</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5265,13 +5261,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5301,46 +5297,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5350,14 +5346,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45469</v>
+        <v>45518</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5370,20 +5366,20 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -5394,58 +5390,58 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5459,10 +5455,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45394</v>
+        <v>45954</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5471,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5515,46 +5511,46 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5568,10 +5564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45518</v>
+        <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5584,10 +5580,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -5596,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5608,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5620,46 +5616,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5673,10 +5669,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44827</v>
+        <v>46007</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5689,7 +5685,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5725,46 +5721,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5778,10 +5774,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46245</v>
+        <v>45712</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5794,13 +5790,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5830,46 +5826,46 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5883,10 +5879,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45810</v>
+        <v>46072</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5899,13 +5895,13 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>4.9</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5939,42 +5935,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5988,10 +5984,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45331</v>
+        <v>46245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6004,7 +6000,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6040,46 +6036,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6089,14 +6085,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45737</v>
+        <v>45325</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6109,7 +6105,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6145,39 +6141,43 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15508-2022</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44662</v>
+        <v>44802</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53144-2021</t>
+          <t>A 15508-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44468</v>
+        <v>44662</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20285-2022</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44698</v>
+        <v>45755</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 53144-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>44468</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 20285-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44967</v>
+        <v>44698</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45307</v>
+        <v>45230</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44949</v>
+        <v>45790</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44662</v>
+        <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45308</v>
+        <v>45329</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45230</v>
+        <v>45091</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44475</v>
+        <v>45306</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45603</v>
+        <v>45596</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44480</v>
+        <v>44805</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>6.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44727</v>
+        <v>44480</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45123</v>
+        <v>44963</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45222</v>
+        <v>44949</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45091</v>
+        <v>44973</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45196</v>
+        <v>44887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44963</v>
+        <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44510</v>
+        <v>45180</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45924</v>
+        <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44523</v>
+        <v>45028</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45894</v>
+        <v>45123</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8343,14 +8343,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46008</v>
+        <v>45394</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44573</v>
+        <v>45535</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44638</v>
+        <v>45924</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44896</v>
+        <v>44475</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8635,14 +8635,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45804</v>
+        <v>45196</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45943</v>
+        <v>45328</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>7.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46154</v>
+        <v>44896</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45947</v>
+        <v>44573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44585</v>
+        <v>44638</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44515</v>
+        <v>44656</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45952</v>
+        <v>45943</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45755</v>
+        <v>44727</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44887</v>
+        <v>44585</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45978</v>
+        <v>45947</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45535</v>
+        <v>45043</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45833</v>
+        <v>45257</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45989</v>
+        <v>45952</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45747</v>
+        <v>45189</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9664,7 +9664,7 @@
         <v>45350</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45994</v>
+        <v>45603</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46002</v>
+        <v>45327</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46002</v>
+        <v>44546</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9895,8 +9895,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9939,7 +9944,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9953,10 +9958,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45327</v>
+        <v>45091</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9969,7 +9974,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10012,7 +10017,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10026,10 +10031,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44546</v>
+        <v>45978</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10041,13 +10046,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10090,7 +10090,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45931</v>
+        <v>45833</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45091</v>
+        <v>45737</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10236,7 +10236,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46036</v>
+        <v>45989</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10309,7 +10309,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45028</v>
+        <v>45307</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46195</v>
+        <v>45994</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10469,10 +10469,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46056</v>
+        <v>45744</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46058</v>
+        <v>45833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.2</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46062</v>
+        <v>45833</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10747,7 +10747,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46062</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46062</v>
+        <v>46002</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10893,7 +10893,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45054</v>
+        <v>46036</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46077</v>
+        <v>46056</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11039,7 +11039,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11053,10 +11053,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44858</v>
+        <v>46058</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11126,10 +11126,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45559</v>
+        <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>8.4</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11185,7 +11185,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44973</v>
+        <v>46062</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>10.5</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11258,7 +11258,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11272,10 +11272,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46118</v>
+        <v>46062</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46134</v>
+        <v>45524</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11404,7 +11404,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 38843-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44802</v>
+        <v>46286</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45306</v>
+        <v>45559</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11564,10 +11564,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45306</v>
+        <v>46077</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11623,7 +11623,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11637,10 +11637,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45523</v>
+        <v>44662</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11696,7 +11696,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 39467-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11710,10 +11710,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45394</v>
+        <v>46288</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11769,7 +11769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11783,10 +11783,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45180</v>
+        <v>45308</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11852,14 +11852,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44636</v>
+        <v>44949</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11915,7 +11915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44805</v>
+        <v>44515</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11998,14 +11998,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44949</v>
+        <v>44636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45744</v>
+        <v>44585</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45596</v>
+        <v>44963</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45524</v>
+        <v>46118</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44656</v>
+        <v>46134</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12363,14 +12363,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45328</v>
+        <v>45804</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.1</v>
+        <v>3.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12426,7 +12426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38843-2026</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46286</v>
+        <v>45054</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44963</v>
+        <v>45306</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44585</v>
+        <v>46008</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12645,7 +12645,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12659,10 +12659,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45329</v>
+        <v>45894</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45790</v>
+        <v>44967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45043</v>
+        <v>44510</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45257</v>
+        <v>45747</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45737</v>
+        <v>46154</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45833</v>
+        <v>45931</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13083,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13170,10 +13170,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45833</v>
+        <v>46195</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13229,24 +13229,24 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>S 2992-2022</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44713</v>
+        <v>45523</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13302,148 +13302,221 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
+          <t>S 2992-2022</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Åtgärd i nyckelbiotop</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="E149" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>S 4359-2024</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D149" s="1" t="n">
+      <c r="D150" s="1" t="n">
         <v>45587</v>
       </c>
-      <c r="E149" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I149" t="n">
+      <c r="E150" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
         <v>1.8</v>
       </c>
-      <c r="J149" t="n">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" t="n">
-        <v>0</v>
-      </c>
-      <c r="T149" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" t="n">
-        <v>0</v>
-      </c>
-      <c r="V149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>S 2388-2025</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D150" s="1" t="n">
+      <c r="D151" s="1" t="n">
         <v>45894</v>
       </c>
-      <c r="E150" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
+      <c r="E151" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
         <v>7.4</v>
       </c>
-      <c r="J150" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
-      <c r="R150" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" s="2" t="inlineStr"/>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 15890-2026</t>
+          <t>A 40059-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46107</v>
+        <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
@@ -1408,12 +1408,244 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>9</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Gropticka
+Talltita
+Blåmossa
+Spillkråka
+Tjäder
+Grönsiska
+Trana
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 40059-2025 artfynd.xlsx", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 40059-2025 karta.png", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 40059-2025 georefererad karta.tif", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 40059-2025 FSC-klagomål.docx", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 40059-2025 FSC-klagomål mail.docx", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 40059-2025 tillsynsbegäran.docx", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 40059-2025 tillsynsbegäran mail.docx", "A 40059-2025")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 40059-2025 prioriterade fågelarter.docx", "A 40059-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 7903-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>20</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita
+Björksplintborre
+Guldlockmossa
+Platt fjädermossa
+Spillkråka
+Kungsfågel
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 15890-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U10" t="n">
         <v>10</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -1425,268 +1657,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 15890-2026 artfynd.xlsx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 15890-2026 karta.png", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 15890-2026 georefererad karta.tif", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 15890-2026 FSC-klagomål.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 15890-2026 FSC-klagomål mail.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 15890-2026 tillsynsbegäran.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 15890-2026 tillsynsbegäran mail.docx", "A 15890-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 15890-2026 prioriterade fågelarter.docx", "A 15890-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 40059-2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45894</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>9</v>
-      </c>
-      <c r="U9" t="n">
-        <v>9</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Gropticka
-Talltita
-Blåmossa
-Spillkråka
-Tjäder
-Grönsiska
-Trana
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 40059-2025 artfynd.xlsx", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 40059-2025 karta.png", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 40059-2025 georefererad karta.tif", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 40059-2025 FSC-klagomål.docx", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 40059-2025 FSC-klagomål mail.docx", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 40059-2025 tillsynsbegäran.docx", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 40059-2025 tillsynsbegäran mail.docx", "A 40059-2025")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 40059-2025 prioriterade fågelarter.docx", "A 40059-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 7903-2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45350</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>20</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita
-Björksplintborre
-Guldlockmossa
-Platt fjädermossa
-Spillkråka
-Kungsfågel
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 7903-2024 artfynd.xlsx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 7903-2024 karta.png", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 7903-2024 georefererad karta.tif", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 7903-2024 FSC-klagomål.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 7903-2024 FSC-klagomål mail.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 7903-2024 tillsynsbegäran.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 7903-2024 tillsynsbegäran mail.docx", "A 7903-2024")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 7903-2024 prioriterade fågelarter.docx", "A 7903-2024")</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 24162-2025</t>
+          <t>A 17684-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45796</v>
+        <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,16 +1839,16 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1872,12 +1872,357 @@
         <v>7</v>
       </c>
       <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Bronshjon
+Havstulpanlav
+Vågbandad barkbock
+Spillkråka
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 17684-2026 artfynd.xlsx", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 17684-2026 karta.png", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 17684-2026 georefererad karta.tif", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 17684-2026 FSC-klagomål.docx", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 17684-2026 FSC-klagomål mail.docx", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 17684-2026 tillsynsbegäran.docx", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 17684-2026 tillsynsbegäran mail.docx", "A 17684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 17684-2026 prioriterade fågelarter.docx", "A 17684-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 60293-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="n">
+        <v>10</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Rödvingetrast
+Stor sotdyna
+Björksplintborre
+Gulnål
+Rostfläck
+Stjärtmes</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 60293-2025 artfynd.xlsx", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 60293-2025 karta.png", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 60293-2025 georefererad karta.tif", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 60293-2025 FSC-klagomål.docx", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 60293-2025 FSC-klagomål mail.docx", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 60293-2025 tillsynsbegäran.docx", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 60293-2025 tillsynsbegäran mail.docx", "A 60293-2025")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 60293-2025 prioriterade fågelarter.docx", "A 60293-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 32151-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>11</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Talltita
+Blåmossa
+Västlig hakmossa
+Spillkråka
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 24162-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45796</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
         <v>19</v>
       </c>
-      <c r="U12" t="n">
+      <c r="U15" t="n">
         <v>19</v>
       </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Blanksvart trämyra
@@ -1888,388 +2233,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 24162-2025 artfynd.xlsx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 24162-2025 karta.png", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 24162-2025 georefererad karta.tif", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 24162-2025 FSC-klagomål.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 24162-2025 FSC-klagomål mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 24162-2025 tillsynsbegäran.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 24162-2025 tillsynsbegäran mail.docx", "A 24162-2025")</f>
         <v/>
       </c>
-      <c r="AE12">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 24162-2025 prioriterade fågelarter.docx", "A 24162-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 17684-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46121</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Bronshjon
-Havstulpanlav
-Vågbandad barkbock
-Spillkråka
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 17684-2026 artfynd.xlsx", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 17684-2026 karta.png", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 17684-2026 georefererad karta.tif", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 17684-2026 FSC-klagomål.docx", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 17684-2026 FSC-klagomål mail.docx", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 17684-2026 tillsynsbegäran.docx", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 17684-2026 tillsynsbegäran mail.docx", "A 17684-2026")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 17684-2026 prioriterade fågelarter.docx", "A 17684-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 60293-2025</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45994</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>10</v>
-      </c>
-      <c r="U14" t="n">
-        <v>10</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Rödvingetrast
-Stor sotdyna
-Björksplintborre
-Gulnål
-Rostfläck
-Stjärtmes</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 60293-2025 artfynd.xlsx", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 60293-2025 karta.png", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 60293-2025 georefererad karta.tif", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 60293-2025 FSC-klagomål.docx", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 60293-2025 FSC-klagomål mail.docx", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 60293-2025 tillsynsbegäran.docx", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 60293-2025 tillsynsbegäran mail.docx", "A 60293-2025")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 60293-2025 prioriterade fågelarter.docx", "A 60293-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 32151-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Talltita
-Blåmossa
-Västlig hakmossa
-Spillkråka
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 32151-2026 artfynd.xlsx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 32151-2026 karta.png", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 32151-2026 georefererad karta.tif", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 32151-2026 FSC-klagomål.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 32151-2026 FSC-klagomål mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 32151-2026 tillsynsbegäran.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 32151-2026 tillsynsbegäran mail.docx", "A 32151-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 32151-2026 prioriterade fågelarter.docx", "A 32151-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26491-2024</t>
+          <t>A 63575-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45469</v>
+        <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,125 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Stor revmossa
+Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26491-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Gulpudrad spiklav
@@ -2346,149 +2459,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 63575-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Stor revmossa
-Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
         <v/>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>45728</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58954-2022</t>
+          <t>A 11516-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,236 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes
+Vildkaprifol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33802-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik
+Björksplintborre
+Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 58954-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44903</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U22" t="n">
         <v>9</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Blåmossa
@@ -2797,260 +3021,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11516-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes
-Vildkaprifol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33802-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik
-Björksplintborre
-Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37461-2024</t>
+          <t>A 14048-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45540</v>
+        <v>46099</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3235,163 +3235,163 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Klippfrullania
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 37461-2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45540</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Gulnål
 Spillkråka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 14048-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46099</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Klippfrullania
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2270-2025</t>
+          <t>A 63569-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45673</v>
+        <v>45275</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3454,1029 +3454,1029 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 13306-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Åkergroda</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 3413-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Vanlig padda
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 12982-2024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Orre
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 1503-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="D32" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>4</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Revlummer</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 13380-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 16534-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
-        <v>45735</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="D33" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>5</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 3413-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>44949</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
-        <v>3</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Vanlig padda
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 13306-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Åkergroda</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 12982-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45385</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Orre
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 16534-2025</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45751</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
         <v/>
       </c>
-      <c r="AE32">
+      <c r="AE33">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 20586-2023</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D33" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>45057</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>1.5</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>3</v>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Entita
 Västlig hakmossa</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
         <v/>
       </c>
-      <c r="AE33">
+      <c r="AE34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 380-2025</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D34" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45662</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>8.6</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U35" t="n">
         <v>2</v>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
         <v/>
       </c>
-      <c r="AE34">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 63569-2023</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
         <v/>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 41607-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44564</v>
+        <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4663,42 +4663,42 @@
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
         <v/>
       </c>
       <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41607-2022</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44827</v>
+        <v>45954</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4764,50 +4764,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41607-2022 artfynd.xlsx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41607-2022 karta.png", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41607-2022 georefererad karta.tif", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41607-2022 FSC-klagomål.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41607-2022 FSC-klagomål mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41607-2022 tillsynsbegäran.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41607-2022 tillsynsbegäran mail.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 41607-2022 prioriterade fågelarter.docx", "A 41607-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45394</v>
+        <v>44564</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4873,50 +4873,50 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41598-2022</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4930,10 +4930,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44827</v>
+        <v>46007</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4982,46 +4982,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45810</v>
+        <v>45712</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>5.7</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5087,46 +5087,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45469</v>
+        <v>45325</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5189,49 +5189,53 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5245,10 +5249,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45331</v>
+        <v>46072</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5261,13 +5265,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5297,46 +5301,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5346,14 +5350,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45518</v>
+        <v>45469</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5366,10 +5370,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5378,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5390,58 +5394,58 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5455,10 +5459,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45954</v>
+        <v>45394</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5471,7 +5475,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5511,46 +5515,46 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5564,10 +5568,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45737</v>
+        <v>45518</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5580,20 +5584,20 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
@@ -5604,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5616,46 +5620,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 41598-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5669,10 +5673,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46007</v>
+        <v>44827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5685,7 +5689,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5721,46 +5725,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 41598-2022 artfynd.xlsx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 41598-2022 karta.png", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 41598-2022 georefererad karta.tif", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 41598-2022 FSC-klagomål.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 41598-2022 FSC-klagomål mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 41598-2022 tillsynsbegäran.docx", "A 41598-2022")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 41598-2022 tillsynsbegäran mail.docx", "A 41598-2022")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5774,10 +5778,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45712</v>
+        <v>46245</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5790,13 +5794,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.7</v>
+        <v>8.5</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5826,46 +5830,46 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5879,10 +5883,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46072</v>
+        <v>45810</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,13 +5899,13 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5935,42 +5939,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5984,10 +5988,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46245</v>
+        <v>45331</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6000,7 +6004,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6036,46 +6040,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6085,14 +6089,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45325</v>
+        <v>45737</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6105,7 +6109,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6141,43 +6145,39 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
-        <v/>
-      </c>
-      <c r="AE51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 15508-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44802</v>
+        <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15508-2022</t>
+          <t>A 53144-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44662</v>
+        <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 20285-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45755</v>
+        <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53144-2021</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44468</v>
+        <v>45189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20285-2022</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44698</v>
+        <v>44967</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45230</v>
+        <v>45307</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45790</v>
+        <v>44662</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44858</v>
+        <v>45308</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45329</v>
+        <v>45230</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45091</v>
+        <v>44475</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45306</v>
+        <v>45603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45596</v>
+        <v>44480</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44805</v>
+        <v>44949</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44480</v>
+        <v>44727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>10</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44963</v>
+        <v>45123</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44949</v>
+        <v>45222</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44973</v>
+        <v>45091</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44887</v>
+        <v>46134</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45222</v>
+        <v>45196</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45180</v>
+        <v>44963</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44523</v>
+        <v>44510</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45028</v>
+        <v>45924</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45123</v>
+        <v>44523</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8343,14 +8343,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45394</v>
+        <v>44573</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45535</v>
+        <v>44638</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45924</v>
+        <v>44896</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44475</v>
+        <v>45943</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45196</v>
+        <v>44585</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45328</v>
+        <v>45947</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44896</v>
+        <v>44515</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44573</v>
+        <v>45952</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44638</v>
+        <v>45894</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44656</v>
+        <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45943</v>
+        <v>45755</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44727</v>
+        <v>44887</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44585</v>
+        <v>45535</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45947</v>
+        <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45043</v>
+        <v>45747</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45257</v>
+        <v>45350</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9511,14 +9511,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45952</v>
+        <v>45804</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45189</v>
+        <v>45833</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45350</v>
+        <v>45989</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45603</v>
+        <v>45327</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45327</v>
+        <v>45994</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44546</v>
+        <v>46154</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9895,13 +9895,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9944,7 +9939,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9958,10 +9953,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45091</v>
+        <v>46002</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9974,7 +9969,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10017,7 +10012,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10031,10 +10026,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45978</v>
+        <v>44546</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10046,8 +10041,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10090,7 +10090,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45833</v>
+        <v>46002</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10163,7 +10163,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10177,10 +10177,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45737</v>
+        <v>45091</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10236,7 +10236,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10250,10 +10250,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45989</v>
+        <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10309,7 +10309,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45307</v>
+        <v>46036</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45994</v>
+        <v>45054</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10455,7 +10455,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10469,10 +10469,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45744</v>
+        <v>46056</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10528,7 +10528,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45833</v>
+        <v>46058</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10601,7 +10601,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10615,10 +10615,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45833</v>
+        <v>46062</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10674,7 +10674,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45833</v>
+        <v>46062</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10747,7 +10747,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46002</v>
+        <v>46062</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10834,10 +10834,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46002</v>
+        <v>44858</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10893,7 +10893,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10907,10 +10907,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46036</v>
+        <v>45559</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10980,10 +10980,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46056</v>
+        <v>46077</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11039,7 +11039,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11053,10 +11053,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46058</v>
+        <v>44973</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11112,7 +11112,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11126,10 +11126,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46062</v>
+        <v>45931</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11185,7 +11185,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46062</v>
+        <v>46118</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11258,7 +11258,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11272,10 +11272,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46062</v>
+        <v>46195</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45524</v>
+        <v>44802</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11404,7 +11404,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38843-2026</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46286</v>
+        <v>46195</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11477,7 +11477,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45559</v>
+        <v>45306</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11550,7 +11550,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11564,10 +11564,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46077</v>
+        <v>45306</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11623,7 +11623,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11633,14 +11633,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44662</v>
+        <v>45394</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11653,7 +11653,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11696,7 +11696,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 39467-2026</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11706,14 +11706,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46288</v>
+        <v>45180</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11769,7 +11769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11779,14 +11779,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45308</v>
+        <v>44636</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11856,10 +11856,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44949</v>
+        <v>45523</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11915,7 +11915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44515</v>
+        <v>44805</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11998,14 +11998,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44636</v>
+        <v>44949</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44585</v>
+        <v>45744</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44963</v>
+        <v>45596</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46118</v>
+        <v>45524</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46134</v>
+        <v>44656</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12363,14 +12363,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45804</v>
+        <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12426,7 +12426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45054</v>
+        <v>44963</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.4</v>
+        <v>4.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45306</v>
+        <v>44585</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 38843-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12586,10 +12586,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46008</v>
+        <v>46286</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12645,7 +12645,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12659,10 +12659,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45894</v>
+        <v>45329</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44967</v>
+        <v>45790</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 39467-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12801,14 +12801,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44510</v>
+        <v>46288</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45747</v>
+        <v>45043</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46154</v>
+        <v>45257</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45931</v>
+        <v>45737</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13083,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13170,10 +13170,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46195</v>
+        <v>45833</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13243,10 +13243,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45523</v>
+        <v>45833</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13319,7 +13319,7 @@
         <v>44713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 63575-2023</t>
+          <t>A 26491-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45275</v>
+        <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,238 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Duvhök
+Gulpudrad spiklav
+Rostfläck
+Sotlav
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 12084-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45728</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka
+Kungsfågel
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 63575-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
         <v>7</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U18" t="n">
         <v>7</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Gulsparv
 Talltita
@@ -2346,262 +2572,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 26491-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45469</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Duvhök
-Gulpudrad spiklav
-Rostfläck
-Sotlav
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 12084-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45728</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>6</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka
-Kungsfågel
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 11516-2026</t>
+          <t>A 58954-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46083</v>
+        <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,124 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp
+Blåmossa
+Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 11516-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
         <v>6</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>6</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Tofsmes
@@ -2797,111 +2909,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 33802-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>46251</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>5.8</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>11</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Kortskaftad ärgspik
 Björksplintborre
@@ -2909,148 +3021,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33802-2026 artfynd.xlsx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33802-2026 karta.png", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33802-2026 georefererad karta.tif", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33802-2026 FSC-klagomål.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33802-2026 FSC-klagomål mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33802-2026 tillsynsbegäran.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33802-2026 tillsynsbegäran mail.docx", "A 33802-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 33802-2026 prioriterade fågelarter.docx", "A 33802-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 58954-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44903</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>9</v>
-      </c>
-      <c r="U22" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp
-Blåmossa
-Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14048-2026</t>
+          <t>A 37461-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3183,10 +3183,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46099</v>
+        <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3235,163 +3235,163 @@
         <v>3</v>
       </c>
       <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Gulnål
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 14048-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Klippfrullania
 Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14048-2026 artfynd.xlsx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14048-2026 karta.png", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14048-2026 georefererad karta.tif", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14048-2026 FSC-klagomål.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14048-2026 FSC-klagomål mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14048-2026 tillsynsbegäran.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14048-2026 tillsynsbegäran mail.docx", "A 14048-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14048-2026 prioriterade fågelarter.docx", "A 14048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 37461-2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45540</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Gulnål
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 37461-2024 artfynd.xlsx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 37461-2024 karta.png", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 37461-2024 georefererad karta.tif", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 37461-2024 FSC-klagomål.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 37461-2024 FSC-klagomål mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 37461-2024 tillsynsbegäran.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 37461-2024 tillsynsbegäran mail.docx", "A 37461-2024")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 37461-2024 prioriterade fågelarter.docx", "A 37461-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63569-2023</t>
+          <t>A 13306-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45275</v>
+        <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3454,1029 +3454,1029 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Större vattensalamander
+Åkergroda</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 1503-2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45306</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
         <v>4</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>4</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 63569-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63569-2023 artfynd.xlsx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63569-2023 karta.png", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63569-2023 georefererad karta.tif", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63569-2023 FSC-klagomål.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63569-2023 FSC-klagomål mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63569-2023 tillsynsbegäran.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63569-2023 tillsynsbegäran mail.docx", "A 63569-2023")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63569-2023 prioriterade fågelarter.docx", "A 63569-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 13306-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 16534-2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>46094</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="D30" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 20586-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45057</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 380-2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>45662</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Större vattensalamander
-Åkergroda</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 13380-2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="X33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 3413-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D28" s="1" t="n">
+      <c r="D34" s="1" t="n">
         <v>44949</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>2.3</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J34" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T34" t="n">
         <v>3</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U34" t="n">
         <v>3</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Vanlig padda
 Revlummer</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 3413-2023 artfynd.xlsx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 3413-2023 karta.png", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 3413-2023 georefererad karta.tif", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 3413-2023 FSC-klagomål.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 3413-2023 FSC-klagomål mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 3413-2023 tillsynsbegäran.docx", "A 3413-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 3413-2023 tillsynsbegäran mail.docx", "A 3413-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 12982-2024</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D35" s="1" t="n">
         <v>45385</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>3.3</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U35" t="n">
         <v>1</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Orre
 Revlummer</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12982-2024 artfynd.xlsx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12982-2024 karta.png", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12982-2024 georefererad karta.tif", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12982-2024 FSC-klagomål.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12982-2024 FSC-klagomål mail.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12982-2024 tillsynsbegäran.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12982-2024 tillsynsbegäran mail.docx", "A 12982-2024")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE35">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12982-2024 prioriterade fågelarter.docx", "A 12982-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 13380-2025</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45735</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>5</v>
-      </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13380-2025 artfynd.xlsx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13380-2025 karta.png", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13380-2025 georefererad karta.tif", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13380-2025 FSC-klagomål.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13380-2025 FSC-klagomål mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13380-2025 tillsynsbegäran.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13380-2025 tillsynsbegäran mail.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 13380-2025 prioriterade fågelarter.docx", "A 13380-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>4</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 16534-2025</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45751</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A 20586-2023</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>45057</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 380-2025</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>45662</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
         <v/>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52423-2025</t>
+          <t>A 14493-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4712,10 +4712,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45954</v>
+        <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4768,46 +4768,46 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 200-2022</t>
+          <t>A 8659-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44564</v>
+        <v>45712</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4873,50 +4873,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62524-2025</t>
+          <t>A 9783-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4930,10 +4926,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46007</v>
+        <v>46072</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4946,7 +4942,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4982,46 +4978,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8659-2025</t>
+          <t>A 26677-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5035,10 +5031,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45712</v>
+        <v>45810</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5051,13 +5047,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5087,46 +5083,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 8659-2025 artfynd.xlsx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 8659-2025 karta.png", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 8659-2025 georefererad karta.tif", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 8659-2025 FSC-klagomål.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 8659-2025 FSC-klagomål mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 8659-2025 tillsynsbegäran.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 8659-2025 tillsynsbegäran mail.docx", "A 8659-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 4363-2024</t>
+          <t>A 52423-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5136,14 +5132,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45325</v>
+        <v>45954</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5156,7 +5152,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5192,50 +5188,50 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 52423-2025 artfynd.xlsx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 52423-2025 karta.png", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 52423-2025 georefererad karta.tif", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 52423-2025 FSC-klagomål.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 52423-2025 FSC-klagomål mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 52423-2025 tillsynsbegäran.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 52423-2025 tillsynsbegäran mail.docx", "A 52423-2025")</f>
         <v/>
       </c>
       <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 52423-2025 prioriterade fågelarter.docx", "A 52423-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9783-2026</t>
+          <t>A 5344-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5249,10 +5245,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46072</v>
+        <v>45331</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5265,13 +5261,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5301,46 +5297,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 9783-2026 artfynd.xlsx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 9783-2026 karta.png", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 9783-2026 georefererad karta.tif", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 9783-2026 FSC-klagomål.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 9783-2026 FSC-klagomål mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 9783-2026 tillsynsbegäran.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 9783-2026 tillsynsbegäran mail.docx", "A 9783-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 26493-2024</t>
+          <t>A 200-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5350,14 +5346,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45469</v>
+        <v>44564</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5370,7 +5366,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5403,49 +5399,53 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 200-2022 artfynd.xlsx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 200-2022 karta.png", "A 200-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 200-2022 georefererad karta.tif", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 200-2022 FSC-klagomål.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 200-2022 FSC-klagomål mail.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 200-2022 tillsynsbegäran.docx", "A 200-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 200-2022 tillsynsbegäran mail.docx", "A 200-2022")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 200-2022 prioriterade fågelarter.docx", "A 200-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14493-2024</t>
+          <t>A 62524-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45394</v>
+        <v>46007</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -5515,46 +5515,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 14493-2024 artfynd.xlsx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 62524-2025 artfynd.xlsx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 14493-2024 karta.png", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 62524-2025 karta.png", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 14493-2024 georefererad karta.tif", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 62524-2025 georefererad karta.tif", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 14493-2024 FSC-klagomål.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 62524-2025 FSC-klagomål.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 14493-2024 FSC-klagomål mail.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 62524-2025 FSC-klagomål mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 14493-2024 tillsynsbegäran.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 62524-2025 tillsynsbegäran.docx", "A 62524-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 14493-2024 tillsynsbegäran mail.docx", "A 14493-2024")</f>
-        <v/>
-      </c>
-      <c r="AE45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 14493-2024 prioriterade fågelarter.docx", "A 14493-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 62524-2025 tillsynsbegäran mail.docx", "A 62524-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33237-2024</t>
+          <t>A 13902-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5568,10 +5564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45518</v>
+        <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5584,10 +5580,10 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -5596,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5608,10 +5604,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5620,39 +5616,39 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
         <v/>
       </c>
     </row>
@@ -5676,7 +5672,7 @@
         <v>44827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5764,7 +5760,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 33142-2026</t>
+          <t>A 26493-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5774,14 +5770,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46245</v>
+        <v>45469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5794,13 +5790,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5827,49 +5823,49 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26493-2024 artfynd.xlsx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26493-2024 karta.png", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26493-2024 georefererad karta.tif", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26493-2024 FSC-klagomål.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26493-2024 FSC-klagomål mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26493-2024 tillsynsbegäran.docx", "A 26493-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26493-2024 tillsynsbegäran mail.docx", "A 26493-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 26677-2025</t>
+          <t>A 33237-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5883,10 +5879,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45810</v>
+        <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5899,20 +5895,20 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -5923,10 +5919,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5939,42 +5935,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26677-2025 artfynd.xlsx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33237-2024 artfynd.xlsx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26677-2025 karta.png", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33237-2024 karta.png", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26677-2025 georefererad karta.tif", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33237-2024 georefererad karta.tif", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26677-2025 FSC-klagomål.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33237-2024 FSC-klagomål.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26677-2025 FSC-klagomål mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33237-2024 FSC-klagomål mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26677-2025 tillsynsbegäran.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33237-2024 tillsynsbegäran.docx", "A 33237-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26677-2025 tillsynsbegäran mail.docx", "A 26677-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33237-2024 tillsynsbegäran mail.docx", "A 33237-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5344-2024</t>
+          <t>A 33142-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5988,10 +5984,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45331</v>
+        <v>46245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6004,7 +6000,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -6040,46 +6036,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 5344-2024 artfynd.xlsx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 33142-2026 artfynd.xlsx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 5344-2024 karta.png", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 33142-2026 karta.png", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 5344-2024 georefererad karta.tif", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 33142-2026 georefererad karta.tif", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 5344-2024 FSC-klagomål.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 33142-2026 FSC-klagomål.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 5344-2024 FSC-klagomål mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 33142-2026 FSC-klagomål mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 5344-2024 tillsynsbegäran.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 33142-2026 tillsynsbegäran.docx", "A 33142-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 5344-2024 tillsynsbegäran mail.docx", "A 5344-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 33142-2026 tillsynsbegäran mail.docx", "A 33142-2026")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13902-2025</t>
+          <t>A 4363-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6089,14 +6085,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45737</v>
+        <v>45325</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6109,7 +6105,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6145,39 +6141,43 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13902-2025 artfynd.xlsx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 4363-2024 artfynd.xlsx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13902-2025 karta.png", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 4363-2024 karta.png", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13902-2025 georefererad karta.tif", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 4363-2024 georefererad karta.tif", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13902-2025 FSC-klagomål.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 4363-2024 FSC-klagomål.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13902-2025 FSC-klagomål mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 4363-2024 FSC-klagomål mail.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13902-2025 tillsynsbegäran.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 4363-2024 tillsynsbegäran.docx", "A 4363-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13902-2025 tillsynsbegäran mail.docx", "A 13902-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 4363-2024 tillsynsbegäran mail.docx", "A 4363-2024")</f>
+        <v/>
+      </c>
+      <c r="AE51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 4363-2024 prioriterade fågelarter.docx", "A 4363-2024")</f>
         <v/>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44429-2023</t>
+          <t>A 53476-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6887,10 +6887,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45189</v>
+        <v>45230</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6916-2023</t>
+          <t>A 26157-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6960,10 +6960,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44967</v>
+        <v>45091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1822-2024</t>
+          <t>A 36763-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45307</v>
+        <v>44805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7092,7 +7092,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15499-2022</t>
+          <t>A 56493-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44662</v>
+        <v>44480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7165,7 +7165,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1960-2024</t>
+          <t>A 5875-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7179,10 +7179,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45308</v>
+        <v>44963</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 53476-2023</t>
+          <t>A 3407-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45230</v>
+        <v>44949</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55405-2021</t>
+          <t>A 51564-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7325,10 +7325,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44475</v>
+        <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7384,7 +7384,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51164-2024</t>
+          <t>A 2414-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7398,10 +7398,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45603</v>
+        <v>46036</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56493-2021</t>
+          <t>A 36403-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7471,10 +7471,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44480</v>
+        <v>45535</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7530,7 +7530,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3418-2023</t>
+          <t>A 55405-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44949</v>
+        <v>44475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 24642-2022</t>
+          <t>A 6621-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7617,10 +7617,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44727</v>
+        <v>46056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>10</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7676,7 +7676,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32762-2023</t>
+          <t>A 7296-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45123</v>
+        <v>46058</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7749,7 +7749,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51564-2023</t>
+          <t>A 8110-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7763,10 +7763,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45222</v>
+        <v>46062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 26157-2023</t>
+          <t>A 8112-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7836,10 +7836,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45091</v>
+        <v>46062</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7895,7 +7895,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19613-2026</t>
+          <t>A 8111-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46134</v>
+        <v>46062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47087-2023</t>
+          <t>A 46227-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45196</v>
+        <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5875-2023</t>
+          <t>A 10459-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44963</v>
+        <v>46077</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 64199-2021</t>
+          <t>A 24642-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8128,10 +8128,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44510</v>
+        <v>44727</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8187,7 +8187,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46227-2025</t>
+          <t>A 57473-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45924</v>
+        <v>44896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8260,7 +8260,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 67160-2021</t>
+          <t>A 1566-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8274,10 +8274,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44523</v>
+        <v>44573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8333,7 +8333,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 1566-2022</t>
+          <t>A 12445-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44573</v>
+        <v>44638</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12445-2022</t>
+          <t>A 50189-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44638</v>
+        <v>45943</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 57473-2022</t>
+          <t>A 50973-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8493,10 +8493,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44896</v>
+        <v>45947</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>12</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8552,7 +8552,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50189-2025</t>
+          <t>A 26083-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45943</v>
+        <v>45091</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3520-2022</t>
+          <t>A 51976-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44585</v>
+        <v>45952</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8698,7 +8698,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50973-2025</t>
+          <t>A 17199-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8712,10 +8712,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45947</v>
+        <v>46118</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8771,7 +8771,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 65226-2021</t>
+          <t>A 56905-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44515</v>
+        <v>45978</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8844,7 +8844,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51976-2025</t>
+          <t>A 19613-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8858,10 +8858,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45952</v>
+        <v>46134</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8917,7 +8917,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 40074-2025</t>
+          <t>A 18637-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45894</v>
+        <v>45043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8990,7 +8990,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62828-2025</t>
+          <t>A 59933-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46008</v>
+        <v>45257</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9063,7 +9063,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17044-2025</t>
+          <t>A 35959-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9077,10 +9077,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45755</v>
+        <v>44802</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9136,7 +9136,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55488-2022</t>
+          <t>A 31407-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44887</v>
+        <v>45833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 36403-2024</t>
+          <t>A 59409-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45535</v>
+        <v>45989</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9282,7 +9282,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 56905-2025</t>
+          <t>A 60287-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9355,7 +9355,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15582-2025</t>
+          <t>A 25840-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9365,14 +9365,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45747</v>
+        <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 7892-2024</t>
+          <t>A 17044-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45350</v>
+        <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9501,7 +9501,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 25840-2025</t>
+          <t>A 61744-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9511,14 +9511,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45804</v>
+        <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 31407-2025</t>
+          <t>A 61771-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9588,10 +9588,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45833</v>
+        <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59409-2025</t>
+          <t>A 62828-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45989</v>
+        <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9720,7 +9720,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4444-2024</t>
+          <t>A 40074-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45327</v>
+        <v>45894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9793,7 +9793,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60287-2025</t>
+          <t>A 48257-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9807,10 +9807,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45994</v>
+        <v>44858</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9866,7 +9866,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22420-2026</t>
+          <t>A 13903-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46154</v>
+        <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 61771-2025</t>
+          <t>A 1687-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9953,10 +9953,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46002</v>
+        <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 72801-2021</t>
+          <t>A 49680-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44546</v>
+        <v>45596</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10041,13 +10041,8 @@
           <t>ALE</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Naturvårdsverket</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10090,7 +10085,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61744-2025</t>
+          <t>A 31409-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10104,10 +10099,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46002</v>
+        <v>45833</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10120,7 +10115,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10163,7 +10158,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26083-2023</t>
+          <t>A 31533-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10177,10 +10172,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45091</v>
+        <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10236,7 +10231,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16344-2023</t>
+          <t>A 31488-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10250,10 +10245,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45028</v>
+        <v>45833</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10266,7 +10261,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10309,7 +10304,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2414-2026</t>
+          <t>A 22420-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10323,10 +10318,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46036</v>
+        <v>46154</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10339,7 +10334,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10382,7 +10377,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20067-2023</t>
+          <t>A 7807-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10396,10 +10391,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45054</v>
+        <v>44973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10412,7 +10407,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>10.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10455,7 +10450,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6621-2026</t>
+          <t>A 55488-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10469,10 +10464,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46056</v>
+        <v>44887</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10485,7 +10480,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10528,7 +10523,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7296-2026</t>
+          <t>A 42446-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10542,10 +10537,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46058</v>
+        <v>45180</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10558,7 +10553,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10601,7 +10596,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8112-2026</t>
+          <t>A 67160-2021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10615,10 +10610,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46062</v>
+        <v>44523</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10631,7 +10626,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10674,7 +10669,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8111-2026</t>
+          <t>A 16344-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10688,10 +10683,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46062</v>
+        <v>45028</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10704,7 +10699,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.3</v>
+        <v>6.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10747,7 +10742,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8110-2026</t>
+          <t>A 32762-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10761,10 +10756,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46062</v>
+        <v>45123</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10777,7 +10772,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10820,7 +10815,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48257-2022</t>
+          <t>A 47728-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10834,10 +10829,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44858</v>
+        <v>45931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10850,7 +10845,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10893,7 +10888,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41309-2024</t>
+          <t>A 14458-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10903,14 +10898,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45559</v>
+        <v>45394</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10923,7 +10918,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>8.4</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10966,7 +10961,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10459-2026</t>
+          <t>A 47087-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10980,10 +10975,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46077</v>
+        <v>45196</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10996,7 +10991,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11039,7 +11034,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 7807-2023</t>
+          <t>A 4642-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11053,10 +11048,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44973</v>
+        <v>45328</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11069,7 +11064,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>10.5</v>
+        <v>7.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11112,7 +11107,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 47728-2025</t>
+          <t>A 28023-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11126,10 +11121,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45931</v>
+        <v>46195</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11142,7 +11137,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11185,7 +11180,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 17199-2026</t>
+          <t>A 28028-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11199,10 +11194,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46118</v>
+        <v>46195</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11215,7 +11210,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11258,7 +11253,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28023-2026</t>
+          <t>A 14731-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11272,10 +11267,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46195</v>
+        <v>44656</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11288,7 +11283,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11331,7 +11326,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 35959-2022</t>
+          <t>A 3520-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11345,10 +11340,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44802</v>
+        <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11361,7 +11356,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11404,7 +11399,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 28028-2026</t>
+          <t>A 44429-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11418,10 +11413,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46195</v>
+        <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11434,7 +11429,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11477,7 +11472,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1500-2024</t>
+          <t>A 7892-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11491,10 +11486,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45306</v>
+        <v>45350</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11507,7 +11502,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11550,7 +11545,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 1687-2024</t>
+          <t>A 51164-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11564,10 +11559,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45306</v>
+        <v>45603</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11580,7 +11575,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11623,7 +11618,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14458-2024</t>
+          <t>A 4444-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11633,14 +11628,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45394</v>
+        <v>45327</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11653,7 +11648,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11696,7 +11691,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 42446-2023</t>
+          <t>A 72801-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11710,10 +11705,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45180</v>
+        <v>44546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11725,8 +11720,13 @@
           <t>ALE</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Naturvårdsverket</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11769,7 +11769,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12055-2022</t>
+          <t>A 34104-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11779,14 +11779,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44636</v>
+        <v>45523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34104-2024</t>
+          <t>A 1822-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11856,10 +11856,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45523</v>
+        <v>45307</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11915,7 +11915,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36763-2022</t>
+          <t>A 15241-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44805</v>
+        <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3407-2023</t>
+          <t>A 34153-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12002,10 +12002,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44949</v>
+        <v>45524</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12061,7 +12061,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15241-2025</t>
+          <t>A 41309-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12075,10 +12075,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45744</v>
+        <v>45559</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12091,7 +12091,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>8.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 49680-2024</t>
+          <t>A 15499-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45596</v>
+        <v>44662</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12207,7 +12207,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34153-2024</t>
+          <t>A 38843-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12221,10 +12221,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45524</v>
+        <v>46286</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14731-2022</t>
+          <t>A 39467-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12290,14 +12290,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44656</v>
+        <v>46288</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12353,7 +12353,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4642-2024</t>
+          <t>A 1960-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45328</v>
+        <v>45308</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.1</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12426,7 +12426,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 5916-2023</t>
+          <t>A 3418-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44963</v>
+        <v>44949</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12499,7 +12499,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3457-2022</t>
+          <t>A 65226-2021</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44585</v>
+        <v>44515</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 38843-2026</t>
+          <t>A 12055-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12582,14 +12582,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46286</v>
+        <v>44636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.7</v>
+        <v>0.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12645,7 +12645,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4971-2024</t>
+          <t>A 3457-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12659,10 +12659,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45329</v>
+        <v>44585</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22946-2025</t>
+          <t>A 5916-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45790</v>
+        <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 39467-2026</t>
+          <t>A 20067-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12801,14 +12801,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46288</v>
+        <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 18637-2023</t>
+          <t>A 1500-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12878,10 +12878,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45043</v>
+        <v>45306</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12937,7 +12937,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 59933-2023</t>
+          <t>A 6916-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12951,10 +12951,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45257</v>
+        <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13010,7 +13010,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 13903-2025</t>
+          <t>A 64199-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13024,10 +13024,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45737</v>
+        <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13083,7 +13083,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31409-2025</t>
+          <t>A 15582-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45833</v>
+        <v>45747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31488-2025</t>
+          <t>A 22946-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13170,10 +13170,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45833</v>
+        <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13229,7 +13229,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 31533-2025</t>
+          <t>A 4971-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13243,10 +13243,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45833</v>
+        <v>45329</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13319,7 +13319,7 @@
         <v>44713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>46083</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45673</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45275</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45751</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>45057</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45662</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44949</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45385</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45712</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46072</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>45810</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45954</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45331</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44564</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46007</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45325</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45230</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44963</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44949</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>46036</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45535</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>46056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>46058</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46062</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>46062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>46077</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44727</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>44638</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45943</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45947</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45091</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45952</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>46118</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45978</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>46134</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45257</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44802</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45989</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45994</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44858</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45596</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45833</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45833</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>46154</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44887</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45180</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44523</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45028</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45123</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45394</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45196</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45328</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>46195</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>46195</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44656</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45350</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45603</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45327</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45307</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45524</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45559</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44662</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>46286</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>46288</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45308</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44949</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44515</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44585</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45306</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45329</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45469</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>45728</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>45275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>44903</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>46083</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>46251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>45673</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45306</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45275</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45751</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>45057</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>45662</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>45735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>44949</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45385</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45595</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>44827</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45394</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45712</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>46072</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>45810</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>45954</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45331</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44564</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
         <v>46007</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45737</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44827</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>45469</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45518</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46245</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>45325</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45011</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
         <v>44504</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>44662</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44468</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>44698</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>45230</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45091</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>44805</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44480</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         <v>44963</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44949</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>46036</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45535</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44475</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>46056</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>46058</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>46062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>46062</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>46062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>46077</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>44727</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44573</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>44638</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45943</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45947</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>45091</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8642,7 +8642,7 @@
         <v>45952</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>46118</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45978</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>46134</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>45043</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>45257</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44802</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45989</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45994</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45755</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>46002</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>46002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>46008</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45894</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44858</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45737</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45306</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45596</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45833</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45833</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45833</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>46154</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>44973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>44887</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45180</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>44523</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45028</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45123</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45931</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45394</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45196</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45328</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>46195</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>46195</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>44656</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45350</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>45603</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>45327</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45307</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45744</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45524</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>45559</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>44662</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12224,7 +12224,7 @@
         <v>46286</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>46288</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45308</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>44949</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>44515</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44585</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12881,7 +12881,7 @@
         <v>45306</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         <v>44510</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>45747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13246,7 +13246,7 @@
         <v>45329</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>44713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13392,7 +13392,7 @@
         <v>45587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>45894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>

--- a/Översikt ALE.xlsx
+++ b/Översikt ALE.xlsx
@@ -601,7 +601,7 @@
         <v>46070</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         <v>45153</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>45357</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>45559</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>45124</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>46062</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>45894</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>45350</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>46107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>45428</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>46121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>45994</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>46235</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>45796</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26491-2024</t>
+          <t>A 63575-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45469</v>
+        <v>45275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,16 +2299,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2332,12 +2332,125 @@
         <v>5</v>
       </c>
       <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gulsparv
+Talltita
+Stor revmossa
+Vågbandad barkbock
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 26491-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45469</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="n">
         <v>8</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Duvhök
 Gulpudrad spiklav
@@ -2346,111 +2459,111 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 26491-2024 artfynd.xlsx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 26491-2024 karta.png", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 26491-2024 georefererad karta.tif", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 26491-2024 FSC-klagomål.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 26491-2024 FSC-klagomål mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 26491-2024 tillsynsbegäran.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 26491-2024 tillsynsbegäran mail.docx", "A 26491-2024")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 26491-2024 prioriterade fågelarter.docx", "A 26491-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 12084-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45728</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>2.4</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>4</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>6</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka
@@ -2459,149 +2572,36 @@
 Äkta lopplummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 12084-2025 artfynd.xlsx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 12084-2025 karta.png", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 12084-2025 georefererad karta.tif", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 12084-2025 FSC-klagomål.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 12084-2025 FSC-klagomål mail.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 12084-2025 tillsynsbegäran.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 12084-2025 tillsynsbegäran mail.docx", "A 12084-2025")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 12084-2025 prioriterade fågelarter.docx", "A 12084-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 63575-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gulsparv
-Talltita
-Stor revmossa
-Vågbandad barkbock
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 63575-2023 artfynd.xlsx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 63575-2023 karta.png", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 63575-2023 georefererad karta.tif", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 63575-2023 FSC-klagomål.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 63575-2023 FSC-klagomål mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 63575-2023 tillsynsbegäran.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 63575-2023 tillsynsbegäran mail.docx", "A 63575-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 63575-2023 prioriterade fågelarter.docx", "A 63575-2023")</f>
         <v/>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         <v>45525</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58954-2022</t>
+          <t>A 11516-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44903</v>
+        <v>46083</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2751,16 +2751,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2784,12 +2784,124 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Tofsmes
+Vildkaprifol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 58954-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44903</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>9</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Dropptaggsvamp
 Blåmossa
@@ -2797,148 +2909,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 58954-2022 artfynd.xlsx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 58954-2022 karta.png", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 58954-2022 georefererad karta.tif", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 58954-2022 FSC-klagomål.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 58954-2022 FSC-klagomål mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 58954-2022 tillsynsbegäran.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 58954-2022 tillsynsbegäran mail.docx", "A 58954-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 58954-2022 prioriterade fågelarter.docx", "A 58954-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 11516-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>6</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Tofsmes
-Vildkaprifol
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 11516-2026 artfynd.xlsx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 11516-2026 karta.png", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 11516-2026 georefererad karta.tif", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 11516-2026 FSC-klagomål.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 11516-2026 FSC-klagomål mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 11516-2026 tillsynsbegäran.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 11516-2026 tillsynsbegäran mail.docx", "A 11516-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 11516-2026 prioriterade fågelarter.docx", "A 11516-2026")</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
         <v>46251</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45123</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>45540</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>46099</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13306-2026</t>
+          <t>A 1503-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3405,10 +3405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46094</v>
+        <v>45306</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>9.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3454,710 +3454,710 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 2270-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45673</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 16534-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45751</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 16534-2025 artfynd.xlsx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 16534-2025 karta.png", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 16534-2025 georefererad karta.tif", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 16534-2025 FSC-klagomål.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 16534-2025 FSC-klagomål mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 16534-2025 tillsynsbegäran.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 16534-2025 tillsynsbegäran mail.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 16534-2025 prioriterade fågelarter.docx", "A 16534-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 20586-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45057</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 20586-2023 artfynd.xlsx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 20586-2023 karta.png", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 20586-2023 georefererad karta.tif", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 20586-2023 FSC-klagomål.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 20586-2023 FSC-klagomål mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 20586-2023 tillsynsbegäran.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 20586-2023 tillsynsbegäran mail.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 20586-2023 prioriterade fågelarter.docx", "A 20586-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 380-2025</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45662</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 380-2025 artfynd.xlsx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 380-2025 karta.png", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 380-2025 georefererad karta.tif", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 380-2025 FSC-klagomål.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 380-2025 FSC-klagomål mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 380-2025 tillsynsbegäran.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 380-2025 tillsynsbegäran mail.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 380-2025 prioriterade fågelarter.docx", "A 380-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 13306-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Större vattensalamander
 Åkergroda</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 13306-2026 artfynd.xlsx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 13306-2026 karta.png", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 13306-2026 georefererad karta.tif", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 13306-2026 FSC-klagomål.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 13306-2026 FSC-klagomål mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 13306-2026 tillsynsbegäran.docx", "A 13306-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 13306-2026 tillsynsbegäran mail.docx", "A 13306-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 2270-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 63569-2023</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D27" s="1" t="n">
-        <v>45673</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="D32" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ALE</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 2270-2025 artfynd.xlsx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 2270-2025 karta.png", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 2270-2025 georefererad karta.tif", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 2270-2025 FSC-klagomål.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 2270-2025 FSC-klagomål mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 2270-2025 tillsynsbegäran.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 2270-2025 tillsynsbegäran mail.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 2270-2025 prioriterade fågelarter.docx", "A 2270-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 1503-2024</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45306</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="T32" t="n">
         <v>4</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U32" t="n">
         <v>4</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/artfynd/A 1503-2024 artfynd.xlsx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor/A 1503-2024 karta.png", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/kartor_geotiff/A 1503-2024 georefererad karta.tif", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomål/A 1503-2024 FSC-klagomål.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/klagomålsmail/A 1503-2024 FSC-klagomål mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsyn/A 1503-2024 tillsynsbegäran.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/tillsynsmail/A 1503-2024 tillsynsbegäran mail.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1440/fåglar/A 1503-2024 prioriterade fågelarter.docx", "A 1503-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 63569-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45275</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ALE</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>